--- a/tools/service_texts_generator2_3CZ1_0.xlsx
+++ b/tools/service_texts_generator2_3CZ1_0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eichler536\github\VDV301tester\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eichler536\github\VDV301tester\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EFC6A1-9AE6-4A5E-AAA6-5F2228155975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D15C63-18DF-4D8F-AF5E-D10FE775C8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Namluvit" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="630">
   <si>
     <t>OIS</t>
   </si>
@@ -1632,18 +1632,9 @@
     <t>mp3</t>
   </si>
   <si>
-    <t>Funkčnost klimatizace</t>
-  </si>
-  <si>
     <t>Nastupujte předními dveřmi</t>
   </si>
   <si>
-    <t>Neprůjezdnost, linka ukončena</t>
-  </si>
-  <si>
-    <t>Neprůjezdnost, odklon</t>
-  </si>
-  <si>
     <t>Přední dveře, předložte doklad</t>
   </si>
   <si>
@@ -1731,77 +1722,19 @@
     <t>&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;</t>
   </si>
   <si>
-    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že konzumace
-potravin není ve vozidlech povolena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not eat any food in the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
-  </si>
-  <si>
     <t>&amp;lt;icon type=&amp;quot;c_Luggage&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;</t>
   </si>
   <si>
-    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že pokládat
-zavazadla na sedadla není dovoleno.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
-  </si>
-  <si>
     <t>&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;</t>
   </si>
   <si>
     <t>&amp;lt;icon type=&amp;quot;c_WheelChair&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;</t>
   </si>
   <si>
-    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
-místo pro invalidní vozík.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a wheelchair.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
-  </si>
-  <si>
     <t>&amp;lt;icon type=&amp;quot;c_Pram&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;</t>
   </si>
   <si>
-    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
-místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
-  </si>
-  <si>
-    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for a mutual transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
-  </si>
-  <si>
-    <t>&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
-&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu silné automobilové dopravy
-pojede tato linka odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;This line will be rerouted due to heavy traffic.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
-&amp;lt;/color&amp;gt;</t>
-  </si>
-  <si>
     <t>&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;</t>
-  </si>
-  <si>
-    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu
-dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled
-departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
-  </si>
-  <si>
-    <t>&amp;lt;icon type=&amp;quot;c_Congestion&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;</t>
-  </si>
-  <si>
-    <t>&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme
-          se za zpoždění linky,
-          které je zapříčiněno silnou individiální
-          dopravou a špatnou průjezdností trasy&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-          &amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are sorry for delay
-          caused by heavy traffic and
-          limited passability of roads.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
-  </si>
-  <si>
-    <t>&amp;lt;icon type=&amp;quot;c_GoFurther&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;</t>
-  </si>
-  <si>
-    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,
-          postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-          &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further
-          into the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
   </si>
   <si>
     <t>icon</t>
@@ -1836,10 +1769,6 @@
   </si>
   <si>
     <t>info o výluce DEMO</t>
-  </si>
-  <si>
-    <t>&amp;lt;font type=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Koh-i-noor – Bělocerkevská&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font type=&amp;quot;48&amp;quot;&amp;gt;Vážení cestující, z důvodu opravy komunikace je linka v tomto úseku odkloněna po náhradní trase. Zastávky Kavkazská, Na Míčánkách a Bělocerkevská jsou vynechány.&amp;lt;/font&amp;gt;</t>
   </si>
   <si>
     <t>trvalá změna DEMO</t>
@@ -1872,40 +1801,6 @@
     <t>&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;</t>
   </si>
   <si>
-    <t>Postupujte dále do vozu</t>
-  </si>
-  <si>
-    <t>Invalidní vozík</t>
-  </si>
-  <si>
-    <t>Kočárek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zákaz jídla a pití </t>
-  </si>
-  <si>
-    <t>Zavazadla</t>
-  </si>
-  <si>
-    <t>Vzájemný přestup</t>
-  </si>
-  <si>
-    <t>Vyčkávání na čas odjezdu</t>
-  </si>
-  <si>
-    <t>&amp;lt;icon type=&amp;quot;c_Bus&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;</t>
-  </si>
-  <si>
-    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přestup z vlakové linky S dle stanovené čekací doby.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for an „S“ train transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
-  </si>
-  <si>
-    <t>&amp;lt;icon type=&amp;quot;c_SBahn&amp;quot;&amp;gt;~&amp;lt;/icon&amp;gt;</t>
-  </si>
-  <si>
-    <t>Vzájemný přestup (vlak)</t>
-  </si>
-  <si>
     <t>Letiště DEMO</t>
   </si>
   <si>
@@ -1923,26 +1818,7 @@
 departures&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
   </si>
   <si>
-    <t>Odklon</t>
-  </si>
-  <si>
-    <t>Zpoždění</t>
-  </si>
-  <si>
     <t>Zpráva z dispečinku DEMO</t>
-  </si>
-  <si>
-    <t>&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
-&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;            
-    Z důvodu sněhové kalamity je ulice Horoměřická neprůjezdná.
-    Linky 316 a 356 jsou ze zastávky Statenice, Černý Vůl, hospoda
-    vedeny odklonem přes zastávky Výhledy, Zemědělská univerzita,
-    V Podbabě a Nádraží Podbaba do zastávky Dejvická (přestup
-    na metro „A“).&amp;lt;br&amp;gt;
-    Pravidelný povoz bude obnoven po zajištění sjízdnosti všech
-    komunikací (během dnešního odpoledne).
-&amp;lt;/font&amp;gt;
-&amp;lt;/color&amp;gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
@@ -1962,13 +1838,183 @@
   <si>
     <t>&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,&amp;lt;br&amp;gt;místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please make room for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,&amp;lt;br&amp;gt;prostor pro invalidní vozík.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please make room for a wheelchair.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>H242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Přepravní kontrola, připravte si cestovní doklady. </t>
+  </si>
+  <si>
+    <t>Klimatizace v provozu, neotevírejte okna.</t>
+  </si>
+  <si>
+    <t>Linka je zde ukončena, neprůjezdnost trasy.</t>
+  </si>
+  <si>
+    <t>Linka je zkrácena, neprůjezdnost trasy.</t>
+  </si>
+  <si>
+    <t>Provoz metra přerušen, použijte náhradní dopravu.</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Provoz metra je přerušen, &amp;lt;br&amp;gt;použijte prosím linky povrchové 
+a náhradní dopravy.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Metro service is suspended.&amp;lt;br&amp;gt;Please use surface transport and replacement lines.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>Provoz tramvají přerušen, použijte náhradní dopravu.</t>
+  </si>
+  <si>
+    <t>Omluva za zpoždění, špatná průjezdnost trasy.</t>
+  </si>
+  <si>
+    <t>H740</t>
+  </si>
+  <si>
+    <t>H741</t>
+  </si>
+  <si>
+    <t>H267</t>
+  </si>
+  <si>
+    <t>H433</t>
+  </si>
+  <si>
+    <t>H148</t>
+  </si>
+  <si>
+    <t>H504</t>
+  </si>
+  <si>
+    <t>H923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nepokládejte zavazadla na sedadla. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvolněte prostor pro kočárek. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvolněte prostor pro invalidní vozík. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvolněte přední dveře, postupte dále do vozu. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vyčkáváme na odjezd dle jízdního řádu. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Přepravní kontrola, výstup pouze předními dveřmi. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kočárek přepravujte na určeném místě. </t>
+  </si>
+  <si>
+    <t>Pes musí být opatřen náhubkem a vodítkem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porucha, vůz dále nepokračuje. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porucha, přestupte do náhradního vozu. </t>
+  </si>
+  <si>
+    <t>Linka jede odklonem, neprůjezdnost trasy.</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Nepokládejte zavazadla na sedadla.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,&amp;lt;br&amp;gt;postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further inside the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Přepravní kontrola, prosíme, připravte si cestovní doklady.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Ticket inspection. Please have your tickets ready.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Pes musí být opatřen náhubkem a vodítkem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Dogs must be kept on a leash and wear a muzzle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for a connecting service.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Provoz tramvají přerušen,&amp;lt;br&amp;gt;použijte prosím linky povrchové a náhradní dopravy.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Tram service is suspended. Please use other surface transport and replacement lines.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Konzumace potravin ve voze není povolena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not eat in the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Kočárek přepravujte&amp;lt;br&amp;gt;na určeném místě.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please keep prams in the designated area.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu technické závady vůz dále nepokračuje.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to a technical failure, this vehicle will not continue its journey.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
+&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu technické závady vůz dále nepokračuje. Prosíme, přestupte do náhradního vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to a technical failure, this vehicle will not continue its journey. Please transfer to a replacement vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu neprůjezdnosti trasy je linka dočasně zkrácena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to an obstruction on the route, this line is shortened.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu neprůjezdnosti trasy je linka vedena odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to an obstruction on the route, this line is diverted.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Koh-i-noor – Bělocerkevská&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;Vážení cestující, z důvodu opravy komunikace je linka v tomto úseku odkloněna po náhradní trase. Zastávky Kavkazská, Na Míčánkách a Bělocerkevská jsou vynechány.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zákaz konzumace potravin ve voze. </t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Klimatizace v provozu, prosíme,&amp;lt;br&amp;gt; neotevírejte okna.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Air conditioning is operating.&amp;lt;br&amp;gt;Please do not open the windows.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme se za zpoždění&amp;lt;br&amp;gt;způsobené špatnou průjezdností trasy.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We apologize for the delay caused by traffic.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;            
+Z důvodu sněhové kalamity je ulice Horoměřická neprůjezdná. Linky 316 a 356 jsou ze zastávky Statenice, Černý Vůl, hospoda vedeny odklonem přes zastávky Výhledy, Zemědělská univerzita, V Podbabě a Nádraží Podbaba do zastávky Dejvická (přestup na metro „A“).&amp;lt;br&amp;gt;Pravidelný povoz bude obnoven po zajištění sjízdnosti všech komunikací (během dnešního odpoledne).
+&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2062,10 +2108,22 @@
     <font>
       <sz val="10"/>
       <color rgb="FF212529"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Consolas"/>
+      <family val="3"/>
       <charset val="238"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2147,7 +2205,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2187,57 +2245,49 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
     <cellStyle name="Normální 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill>
@@ -2668,15 +2718,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C179"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="141.85546875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="10.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="141.88671875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" customFormat="1" ht="19.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -2687,7 +2737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" customFormat="1" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A2" s="13" t="s">
         <v>163</v>
       </c>
@@ -2696,7 +2746,7 @@
       </c>
       <c r="C2" s="11"/>
     </row>
-    <row r="3" spans="1:3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" customFormat="1" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A3" s="13" t="s">
         <v>166</v>
       </c>
@@ -2705,7 +2755,7 @@
       </c>
       <c r="C3" s="11"/>
     </row>
-    <row r="4" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A4" s="13" t="s">
         <v>167</v>
       </c>
@@ -2714,7 +2764,7 @@
       </c>
       <c r="C4" s="11"/>
     </row>
-    <row r="5" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A5" s="13" t="s">
         <v>170</v>
       </c>
@@ -2723,7 +2773,7 @@
       </c>
       <c r="C5" s="11"/>
     </row>
-    <row r="6" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A6" s="13" t="s">
         <v>171</v>
       </c>
@@ -2732,7 +2782,7 @@
       </c>
       <c r="C6" s="11"/>
     </row>
-    <row r="7" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A7" s="13" t="s">
         <v>173</v>
       </c>
@@ -2741,7 +2791,7 @@
       </c>
       <c r="C7" s="11"/>
     </row>
-    <row r="8" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A8" s="13" t="s">
         <v>175</v>
       </c>
@@ -2750,7 +2800,7 @@
       </c>
       <c r="C8" s="11"/>
     </row>
-    <row r="9" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A9" s="13" t="s">
         <v>176</v>
       </c>
@@ -2759,7 +2809,7 @@
       </c>
       <c r="C9" s="11"/>
     </row>
-    <row r="10" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A10" s="13" t="s">
         <v>177</v>
       </c>
@@ -2768,7 +2818,7 @@
       </c>
       <c r="C10" s="11"/>
     </row>
-    <row r="11" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A11" s="13" t="s">
         <v>178</v>
       </c>
@@ -2777,7 +2827,7 @@
       </c>
       <c r="C11" s="11"/>
     </row>
-    <row r="12" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A12" s="13" t="s">
         <v>183</v>
       </c>
@@ -2786,7 +2836,7 @@
       </c>
       <c r="C12" s="11"/>
     </row>
-    <row r="13" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A13" s="13" t="s">
         <v>185</v>
       </c>
@@ -2795,7 +2845,7 @@
       </c>
       <c r="C13" s="11"/>
     </row>
-    <row r="14" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A14" s="13" t="s">
         <v>187</v>
       </c>
@@ -2804,7 +2854,7 @@
       </c>
       <c r="C14" s="11"/>
     </row>
-    <row r="15" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A15" s="13" t="s">
         <v>189</v>
       </c>
@@ -2813,7 +2863,7 @@
       </c>
       <c r="C15" s="11"/>
     </row>
-    <row r="16" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A16" s="13" t="s">
         <v>191</v>
       </c>
@@ -2822,7 +2872,7 @@
       </c>
       <c r="C16" s="11"/>
     </row>
-    <row r="17" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A17" s="13" t="s">
         <v>193</v>
       </c>
@@ -2831,7 +2881,7 @@
       </c>
       <c r="C17" s="11"/>
     </row>
-    <row r="18" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A18" s="13" t="s">
         <v>195</v>
       </c>
@@ -2840,7 +2890,7 @@
       </c>
       <c r="C18" s="11"/>
     </row>
-    <row r="19" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A19" s="13" t="s">
         <v>197</v>
       </c>
@@ -2849,7 +2899,7 @@
       </c>
       <c r="C19" s="11"/>
     </row>
-    <row r="20" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A20" s="13" t="s">
         <v>199</v>
       </c>
@@ -2858,7 +2908,7 @@
       </c>
       <c r="C20" s="11"/>
     </row>
-    <row r="21" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A21" s="13" t="s">
         <v>201</v>
       </c>
@@ -2867,7 +2917,7 @@
       </c>
       <c r="C21" s="11"/>
     </row>
-    <row r="22" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A22" s="13" t="s">
         <v>203</v>
       </c>
@@ -2876,7 +2926,7 @@
       </c>
       <c r="C22" s="11"/>
     </row>
-    <row r="23" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A23" s="13" t="s">
         <v>205</v>
       </c>
@@ -2885,7 +2935,7 @@
       </c>
       <c r="C23" s="11"/>
     </row>
-    <row r="24" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
         <v>207</v>
       </c>
@@ -2894,7 +2944,7 @@
       </c>
       <c r="C24" s="11"/>
     </row>
-    <row r="25" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A25" s="13" t="s">
         <v>209</v>
       </c>
@@ -2903,7 +2953,7 @@
       </c>
       <c r="C25" s="11"/>
     </row>
-    <row r="26" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A26" s="13" t="s">
         <v>211</v>
       </c>
@@ -2912,7 +2962,7 @@
       </c>
       <c r="C26" s="11"/>
     </row>
-    <row r="27" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A27" s="13" t="s">
         <v>213</v>
       </c>
@@ -2921,7 +2971,7 @@
       </c>
       <c r="C27" s="11"/>
     </row>
-    <row r="28" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A28" s="13" t="s">
         <v>215</v>
       </c>
@@ -2930,7 +2980,7 @@
       </c>
       <c r="C28" s="11"/>
     </row>
-    <row r="29" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A29" s="13" t="s">
         <v>217</v>
       </c>
@@ -2939,7 +2989,7 @@
       </c>
       <c r="C29" s="11"/>
     </row>
-    <row r="30" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A30" s="13" t="s">
         <v>219</v>
       </c>
@@ -2948,7 +2998,7 @@
       </c>
       <c r="C30" s="11"/>
     </row>
-    <row r="31" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A31" s="13" t="s">
         <v>221</v>
       </c>
@@ -2957,7 +3007,7 @@
       </c>
       <c r="C31" s="11"/>
     </row>
-    <row r="32" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A32" s="13" t="s">
         <v>223</v>
       </c>
@@ -2966,7 +3016,7 @@
       </c>
       <c r="C32" s="11"/>
     </row>
-    <row r="33" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A33" s="13" t="s">
         <v>225</v>
       </c>
@@ -2975,7 +3025,7 @@
       </c>
       <c r="C33" s="11"/>
     </row>
-    <row r="34" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A34" s="13" t="s">
         <v>227</v>
       </c>
@@ -2984,7 +3034,7 @@
       </c>
       <c r="C34" s="11"/>
     </row>
-    <row r="35" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A35" s="13" t="s">
         <v>229</v>
       </c>
@@ -2993,7 +3043,7 @@
       </c>
       <c r="C35" s="11"/>
     </row>
-    <row r="36" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A36" s="13" t="s">
         <v>231</v>
       </c>
@@ -3002,7 +3052,7 @@
       </c>
       <c r="C36" s="11"/>
     </row>
-    <row r="37" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A37" s="13" t="s">
         <v>233</v>
       </c>
@@ -3011,7 +3061,7 @@
       </c>
       <c r="C37" s="11"/>
     </row>
-    <row r="38" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A38" s="13" t="s">
         <v>235</v>
       </c>
@@ -3020,7 +3070,7 @@
       </c>
       <c r="C38" s="11"/>
     </row>
-    <row r="39" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A39" s="13" t="s">
         <v>237</v>
       </c>
@@ -3029,7 +3079,7 @@
       </c>
       <c r="C39" s="11"/>
     </row>
-    <row r="40" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A40" s="13" t="s">
         <v>239</v>
       </c>
@@ -3038,7 +3088,7 @@
       </c>
       <c r="C40" s="11"/>
     </row>
-    <row r="41" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A41" s="13" t="s">
         <v>241</v>
       </c>
@@ -3047,7 +3097,7 @@
       </c>
       <c r="C41" s="11"/>
     </row>
-    <row r="42" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A42" s="13" t="s">
         <v>243</v>
       </c>
@@ -3056,7 +3106,7 @@
       </c>
       <c r="C42" s="11"/>
     </row>
-    <row r="43" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A43" s="13" t="s">
         <v>245</v>
       </c>
@@ -3065,7 +3115,7 @@
       </c>
       <c r="C43" s="11"/>
     </row>
-    <row r="44" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A44" s="13" t="s">
         <v>247</v>
       </c>
@@ -3074,7 +3124,7 @@
       </c>
       <c r="C44" s="11"/>
     </row>
-    <row r="45" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A45" s="13" t="s">
         <v>249</v>
       </c>
@@ -3083,7 +3133,7 @@
       </c>
       <c r="C45" s="11"/>
     </row>
-    <row r="46" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A46" s="13" t="s">
         <v>251</v>
       </c>
@@ -3092,7 +3142,7 @@
       </c>
       <c r="C46" s="11"/>
     </row>
-    <row r="47" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A47" s="13" t="s">
         <v>253</v>
       </c>
@@ -3101,7 +3151,7 @@
       </c>
       <c r="C47" s="11"/>
     </row>
-    <row r="48" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A48" s="13" t="s">
         <v>255</v>
       </c>
@@ -3110,7 +3160,7 @@
       </c>
       <c r="C48" s="11"/>
     </row>
-    <row r="49" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A49" s="13" t="s">
         <v>257</v>
       </c>
@@ -3119,7 +3169,7 @@
       </c>
       <c r="C49" s="11"/>
     </row>
-    <row r="50" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A50" s="13" t="s">
         <v>259</v>
       </c>
@@ -3128,7 +3178,7 @@
       </c>
       <c r="C50" s="11"/>
     </row>
-    <row r="51" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A51" s="13" t="s">
         <v>261</v>
       </c>
@@ -3137,7 +3187,7 @@
       </c>
       <c r="C51" s="11"/>
     </row>
-    <row r="52" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A52" s="13" t="s">
         <v>263</v>
       </c>
@@ -3146,7 +3196,7 @@
       </c>
       <c r="C52" s="11"/>
     </row>
-    <row r="53" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A53" s="13" t="s">
         <v>265</v>
       </c>
@@ -3155,7 +3205,7 @@
       </c>
       <c r="C53" s="11"/>
     </row>
-    <row r="54" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A54" s="13" t="s">
         <v>267</v>
       </c>
@@ -3164,7 +3214,7 @@
       </c>
       <c r="C54" s="11"/>
     </row>
-    <row r="55" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A55" s="13" t="s">
         <v>269</v>
       </c>
@@ -3173,7 +3223,7 @@
       </c>
       <c r="C55" s="11"/>
     </row>
-    <row r="56" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A56" s="13" t="s">
         <v>271</v>
       </c>
@@ -3182,7 +3232,7 @@
       </c>
       <c r="C56" s="11"/>
     </row>
-    <row r="57" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A57" s="13" t="s">
         <v>273</v>
       </c>
@@ -3191,7 +3241,7 @@
       </c>
       <c r="C57" s="11"/>
     </row>
-    <row r="58" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A58" s="13" t="s">
         <v>275</v>
       </c>
@@ -3200,7 +3250,7 @@
       </c>
       <c r="C58" s="11"/>
     </row>
-    <row r="59" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A59" s="13" t="s">
         <v>277</v>
       </c>
@@ -3209,7 +3259,7 @@
       </c>
       <c r="C59" s="11"/>
     </row>
-    <row r="60" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A60" s="13" t="s">
         <v>279</v>
       </c>
@@ -3218,7 +3268,7 @@
       </c>
       <c r="C60" s="11"/>
     </row>
-    <row r="61" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A61" s="13" t="s">
         <v>281</v>
       </c>
@@ -3227,7 +3277,7 @@
       </c>
       <c r="C61" s="11"/>
     </row>
-    <row r="62" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A62" s="13" t="s">
         <v>283</v>
       </c>
@@ -3236,7 +3286,7 @@
       </c>
       <c r="C62" s="11"/>
     </row>
-    <row r="63" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A63" s="13" t="s">
         <v>285</v>
       </c>
@@ -3245,7 +3295,7 @@
       </c>
       <c r="C63" s="11"/>
     </row>
-    <row r="64" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A64" s="13" t="s">
         <v>287</v>
       </c>
@@ -3254,7 +3304,7 @@
       </c>
       <c r="C64" s="11"/>
     </row>
-    <row r="65" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A65" s="13" t="s">
         <v>289</v>
       </c>
@@ -3263,7 +3313,7 @@
       </c>
       <c r="C65" s="11"/>
     </row>
-    <row r="66" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A66" s="13" t="s">
         <v>291</v>
       </c>
@@ -3272,7 +3322,7 @@
       </c>
       <c r="C66" s="11"/>
     </row>
-    <row r="67" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A67" s="13" t="s">
         <v>293</v>
       </c>
@@ -3281,7 +3331,7 @@
       </c>
       <c r="C67" s="11"/>
     </row>
-    <row r="68" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A68" s="13" t="s">
         <v>295</v>
       </c>
@@ -3290,7 +3340,7 @@
       </c>
       <c r="C68" s="11"/>
     </row>
-    <row r="69" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A69" s="13" t="s">
         <v>297</v>
       </c>
@@ -3299,7 +3349,7 @@
       </c>
       <c r="C69" s="11"/>
     </row>
-    <row r="70" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A70" s="13" t="s">
         <v>299</v>
       </c>
@@ -3308,7 +3358,7 @@
       </c>
       <c r="C70" s="11"/>
     </row>
-    <row r="71" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A71" s="13" t="s">
         <v>301</v>
       </c>
@@ -3317,7 +3367,7 @@
       </c>
       <c r="C71" s="11"/>
     </row>
-    <row r="72" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A72" s="13" t="s">
         <v>303</v>
       </c>
@@ -3326,7 +3376,7 @@
       </c>
       <c r="C72" s="11"/>
     </row>
-    <row r="73" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A73" s="13" t="s">
         <v>305</v>
       </c>
@@ -3335,7 +3385,7 @@
       </c>
       <c r="C73" s="11"/>
     </row>
-    <row r="74" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A74" s="13" t="s">
         <v>307</v>
       </c>
@@ -3344,7 +3394,7 @@
       </c>
       <c r="C74" s="11"/>
     </row>
-    <row r="75" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A75" s="13" t="s">
         <v>309</v>
       </c>
@@ -3353,7 +3403,7 @@
       </c>
       <c r="C75" s="11"/>
     </row>
-    <row r="76" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A76" s="13" t="s">
         <v>311</v>
       </c>
@@ -3362,7 +3412,7 @@
       </c>
       <c r="C76" s="11"/>
     </row>
-    <row r="77" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A77" s="13" t="s">
         <v>313</v>
       </c>
@@ -3371,7 +3421,7 @@
       </c>
       <c r="C77" s="11"/>
     </row>
-    <row r="78" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A78" s="13" t="s">
         <v>315</v>
       </c>
@@ -3380,7 +3430,7 @@
       </c>
       <c r="C78" s="11"/>
     </row>
-    <row r="79" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A79" s="13" t="s">
         <v>317</v>
       </c>
@@ -3391,7 +3441,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A80" s="13" t="s">
         <v>320</v>
       </c>
@@ -3400,7 +3450,7 @@
       </c>
       <c r="C80" s="11"/>
     </row>
-    <row r="81" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A81" s="13" t="s">
         <v>322</v>
       </c>
@@ -3409,7 +3459,7 @@
       </c>
       <c r="C81" s="11"/>
     </row>
-    <row r="82" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A82" s="13" t="s">
         <v>324</v>
       </c>
@@ -3418,7 +3468,7 @@
       </c>
       <c r="C82" s="11"/>
     </row>
-    <row r="83" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A83" s="13" t="s">
         <v>326</v>
       </c>
@@ -3427,7 +3477,7 @@
       </c>
       <c r="C83" s="11"/>
     </row>
-    <row r="84" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A84" s="13" t="s">
         <v>328</v>
       </c>
@@ -3436,7 +3486,7 @@
       </c>
       <c r="C84" s="11"/>
     </row>
-    <row r="85" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A85" s="13" t="s">
         <v>330</v>
       </c>
@@ -3445,7 +3495,7 @@
       </c>
       <c r="C85" s="11"/>
     </row>
-    <row r="86" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A86" s="13" t="s">
         <v>332</v>
       </c>
@@ -3454,7 +3504,7 @@
       </c>
       <c r="C86" s="11"/>
     </row>
-    <row r="87" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A87" s="13" t="s">
         <v>334</v>
       </c>
@@ -3463,7 +3513,7 @@
       </c>
       <c r="C87" s="11"/>
     </row>
-    <row r="88" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A88" s="13" t="s">
         <v>336</v>
       </c>
@@ -3472,7 +3522,7 @@
       </c>
       <c r="C88" s="11"/>
     </row>
-    <row r="89" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A89" s="13" t="s">
         <v>338</v>
       </c>
@@ -3481,7 +3531,7 @@
       </c>
       <c r="C89" s="11"/>
     </row>
-    <row r="90" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A90" s="13" t="s">
         <v>340</v>
       </c>
@@ -3490,7 +3540,7 @@
       </c>
       <c r="C90" s="11"/>
     </row>
-    <row r="91" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A91" s="13" t="s">
         <v>342</v>
       </c>
@@ -3499,7 +3549,7 @@
       </c>
       <c r="C91" s="11"/>
     </row>
-    <row r="92" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A92" s="13" t="s">
         <v>344</v>
       </c>
@@ -3508,7 +3558,7 @@
       </c>
       <c r="C92" s="11"/>
     </row>
-    <row r="93" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A93" s="13" t="s">
         <v>346</v>
       </c>
@@ -3517,7 +3567,7 @@
       </c>
       <c r="C93" s="11"/>
     </row>
-    <row r="94" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A94" s="13" t="s">
         <v>348</v>
       </c>
@@ -3526,7 +3576,7 @@
       </c>
       <c r="C94" s="11"/>
     </row>
-    <row r="95" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A95" s="13" t="s">
         <v>350</v>
       </c>
@@ -3535,7 +3585,7 @@
       </c>
       <c r="C95" s="11"/>
     </row>
-    <row r="96" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A96" s="13" t="s">
         <v>352</v>
       </c>
@@ -3544,7 +3594,7 @@
       </c>
       <c r="C96" s="11"/>
     </row>
-    <row r="97" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A97" s="13" t="s">
         <v>354</v>
       </c>
@@ -3553,7 +3603,7 @@
       </c>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A98" s="13" t="s">
         <v>356</v>
       </c>
@@ -3562,7 +3612,7 @@
       </c>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A99" s="13" t="s">
         <v>358</v>
       </c>
@@ -3571,7 +3621,7 @@
       </c>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A100" s="13" t="s">
         <v>360</v>
       </c>
@@ -3580,7 +3630,7 @@
       </c>
       <c r="C100" s="11"/>
     </row>
-    <row r="101" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A101" s="13" t="s">
         <v>362</v>
       </c>
@@ -3589,7 +3639,7 @@
       </c>
       <c r="C101" s="11"/>
     </row>
-    <row r="102" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A102" s="13" t="s">
         <v>363</v>
       </c>
@@ -3598,7 +3648,7 @@
       </c>
       <c r="C102" s="11"/>
     </row>
-    <row r="103" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A103" s="13" t="s">
         <v>365</v>
       </c>
@@ -3607,7 +3657,7 @@
       </c>
       <c r="C103" s="11"/>
     </row>
-    <row r="104" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A104" s="13" t="s">
         <v>367</v>
       </c>
@@ -3616,7 +3666,7 @@
       </c>
       <c r="C104" s="11"/>
     </row>
-    <row r="105" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A105" s="13" t="s">
         <v>369</v>
       </c>
@@ -3625,7 +3675,7 @@
       </c>
       <c r="C105" s="11"/>
     </row>
-    <row r="106" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A106" s="13" t="s">
         <v>371</v>
       </c>
@@ -3634,7 +3684,7 @@
       </c>
       <c r="C106" s="11"/>
     </row>
-    <row r="107" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A107" s="13" t="s">
         <v>373</v>
       </c>
@@ -3643,7 +3693,7 @@
       </c>
       <c r="C107" s="11"/>
     </row>
-    <row r="108" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A108" s="13" t="s">
         <v>375</v>
       </c>
@@ -3652,7 +3702,7 @@
       </c>
       <c r="C108" s="11"/>
     </row>
-    <row r="109" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A109" s="13" t="s">
         <v>377</v>
       </c>
@@ -3661,7 +3711,7 @@
       </c>
       <c r="C109" s="11"/>
     </row>
-    <row r="110" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A110" s="13" t="s">
         <v>379</v>
       </c>
@@ -3670,7 +3720,7 @@
       </c>
       <c r="C110" s="11"/>
     </row>
-    <row r="111" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A111" s="13" t="s">
         <v>381</v>
       </c>
@@ -3679,7 +3729,7 @@
       </c>
       <c r="C111" s="11"/>
     </row>
-    <row r="112" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A112" s="13" t="s">
         <v>383</v>
       </c>
@@ -3688,7 +3738,7 @@
       </c>
       <c r="C112" s="11"/>
     </row>
-    <row r="113" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A113" s="13" t="s">
         <v>385</v>
       </c>
@@ -3697,7 +3747,7 @@
       </c>
       <c r="C113" s="11"/>
     </row>
-    <row r="114" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A114" s="13" t="s">
         <v>387</v>
       </c>
@@ -3706,7 +3756,7 @@
       </c>
       <c r="C114" s="11"/>
     </row>
-    <row r="115" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A115" s="13" t="s">
         <v>389</v>
       </c>
@@ -3715,7 +3765,7 @@
       </c>
       <c r="C115" s="11"/>
     </row>
-    <row r="116" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A116" s="13" t="s">
         <v>391</v>
       </c>
@@ -3724,7 +3774,7 @@
       </c>
       <c r="C116" s="11"/>
     </row>
-    <row r="117" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A117" s="13" t="s">
         <v>393</v>
       </c>
@@ -3733,7 +3783,7 @@
       </c>
       <c r="C117" s="11"/>
     </row>
-    <row r="118" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A118" s="13" t="s">
         <v>395</v>
       </c>
@@ -3742,7 +3792,7 @@
       </c>
       <c r="C118" s="11"/>
     </row>
-    <row r="119" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A119" s="13" t="s">
         <v>395</v>
       </c>
@@ -3751,7 +3801,7 @@
       </c>
       <c r="C119" s="11"/>
     </row>
-    <row r="120" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A120" s="13" t="s">
         <v>398</v>
       </c>
@@ -3760,7 +3810,7 @@
       </c>
       <c r="C120" s="11"/>
     </row>
-    <row r="121" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A121" s="13" t="s">
         <v>400</v>
       </c>
@@ -3769,7 +3819,7 @@
       </c>
       <c r="C121" s="11"/>
     </row>
-    <row r="122" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A122" s="13" t="s">
         <v>402</v>
       </c>
@@ -3778,7 +3828,7 @@
       </c>
       <c r="C122" s="11"/>
     </row>
-    <row r="123" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A123" s="13" t="s">
         <v>404</v>
       </c>
@@ -3787,7 +3837,7 @@
       </c>
       <c r="C123" s="11"/>
     </row>
-    <row r="124" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A124" s="13" t="s">
         <v>406</v>
       </c>
@@ -3796,7 +3846,7 @@
       </c>
       <c r="C124" s="11"/>
     </row>
-    <row r="125" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A125" s="13" t="s">
         <v>408</v>
       </c>
@@ -3805,7 +3855,7 @@
       </c>
       <c r="C125" s="11"/>
     </row>
-    <row r="126" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A126" s="13" t="s">
         <v>410</v>
       </c>
@@ -3814,7 +3864,7 @@
       </c>
       <c r="C126" s="11"/>
     </row>
-    <row r="127" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A127" s="13" t="s">
         <v>412</v>
       </c>
@@ -3825,7 +3875,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A128" s="13" t="s">
         <v>415</v>
       </c>
@@ -3834,7 +3884,7 @@
       </c>
       <c r="C128" s="11"/>
     </row>
-    <row r="129" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A129" s="13" t="s">
         <v>417</v>
       </c>
@@ -3843,7 +3893,7 @@
       </c>
       <c r="C129" s="11"/>
     </row>
-    <row r="130" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A130" s="13" t="s">
         <v>419</v>
       </c>
@@ -3852,7 +3902,7 @@
       </c>
       <c r="C130" s="11"/>
     </row>
-    <row r="131" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A131" s="13" t="s">
         <v>421</v>
       </c>
@@ -3861,7 +3911,7 @@
       </c>
       <c r="C131" s="11"/>
     </row>
-    <row r="132" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A132" s="13" t="s">
         <v>423</v>
       </c>
@@ -3870,7 +3920,7 @@
       </c>
       <c r="C132" s="11"/>
     </row>
-    <row r="133" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A133" s="13" t="s">
         <v>425</v>
       </c>
@@ -3879,7 +3929,7 @@
       </c>
       <c r="C133" s="11"/>
     </row>
-    <row r="134" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A134" s="13" t="s">
         <v>426</v>
       </c>
@@ -3888,7 +3938,7 @@
       </c>
       <c r="C134" s="11"/>
     </row>
-    <row r="135" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A135" s="13" t="s">
         <v>428</v>
       </c>
@@ -3897,7 +3947,7 @@
       </c>
       <c r="C135" s="11"/>
     </row>
-    <row r="136" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A136" s="13" t="s">
         <v>430</v>
       </c>
@@ -3908,7 +3958,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A137" s="13" t="s">
         <v>432</v>
       </c>
@@ -3917,7 +3967,7 @@
       </c>
       <c r="C137" s="11"/>
     </row>
-    <row r="138" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A138" s="13" t="s">
         <v>434</v>
       </c>
@@ -3926,7 +3976,7 @@
       </c>
       <c r="C138" s="11"/>
     </row>
-    <row r="139" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A139" s="13" t="s">
         <v>436</v>
       </c>
@@ -3935,7 +3985,7 @@
       </c>
       <c r="C139" s="11"/>
     </row>
-    <row r="140" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A140" s="13" t="s">
         <v>438</v>
       </c>
@@ -3944,7 +3994,7 @@
       </c>
       <c r="C140" s="11"/>
     </row>
-    <row r="141" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A141" s="13" t="s">
         <v>439</v>
       </c>
@@ -3953,7 +4003,7 @@
       </c>
       <c r="C141" s="11"/>
     </row>
-    <row r="142" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A142" s="13" t="s">
         <v>515</v>
       </c>
@@ -3962,7 +4012,7 @@
       </c>
       <c r="C142" s="11"/>
     </row>
-    <row r="143" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A143" s="13" t="s">
         <v>516</v>
       </c>
@@ -3971,7 +4021,7 @@
       </c>
       <c r="C143" s="11"/>
     </row>
-    <row r="144" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A144" s="13" t="s">
         <v>441</v>
       </c>
@@ -3980,7 +4030,7 @@
       </c>
       <c r="C144" s="11"/>
     </row>
-    <row r="145" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A145" s="13" t="s">
         <v>443</v>
       </c>
@@ -3989,7 +4039,7 @@
       </c>
       <c r="C145" s="11"/>
     </row>
-    <row r="146" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A146" s="13" t="s">
         <v>445</v>
       </c>
@@ -3998,7 +4048,7 @@
       </c>
       <c r="C146" s="11"/>
     </row>
-    <row r="147" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A147" s="13" t="s">
         <v>447</v>
       </c>
@@ -4007,7 +4057,7 @@
       </c>
       <c r="C147" s="11"/>
     </row>
-    <row r="148" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A148" s="13" t="s">
         <v>449</v>
       </c>
@@ -4016,7 +4066,7 @@
       </c>
       <c r="C148" s="11"/>
     </row>
-    <row r="149" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A149" s="13" t="s">
         <v>451</v>
       </c>
@@ -4025,7 +4075,7 @@
       </c>
       <c r="C149" s="11"/>
     </row>
-    <row r="150" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A150" s="13" t="s">
         <v>453</v>
       </c>
@@ -4034,7 +4084,7 @@
       </c>
       <c r="C150" s="11"/>
     </row>
-    <row r="151" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A151" s="13" t="s">
         <v>455</v>
       </c>
@@ -4043,7 +4093,7 @@
       </c>
       <c r="C151" s="11"/>
     </row>
-    <row r="152" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A152" s="13" t="s">
         <v>457</v>
       </c>
@@ -4052,7 +4102,7 @@
       </c>
       <c r="C152" s="11"/>
     </row>
-    <row r="153" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A153" s="13" t="s">
         <v>459</v>
       </c>
@@ -4061,7 +4111,7 @@
       </c>
       <c r="C153" s="11"/>
     </row>
-    <row r="154" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A154" s="13" t="s">
         <v>461</v>
       </c>
@@ -4070,7 +4120,7 @@
       </c>
       <c r="C154" s="11"/>
     </row>
-    <row r="155" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A155" s="13" t="s">
         <v>463</v>
       </c>
@@ -4081,7 +4131,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A156" s="13" t="s">
         <v>465</v>
       </c>
@@ -4090,7 +4140,7 @@
       </c>
       <c r="C156" s="11"/>
     </row>
-    <row r="157" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A157" s="13" t="s">
         <v>467</v>
       </c>
@@ -4099,7 +4149,7 @@
       </c>
       <c r="C157" s="11"/>
     </row>
-    <row r="158" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A158" s="13" t="s">
         <v>469</v>
       </c>
@@ -4108,7 +4158,7 @@
       </c>
       <c r="C158" s="11"/>
     </row>
-    <row r="159" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A159" s="13" t="s">
         <v>471</v>
       </c>
@@ -4117,7 +4167,7 @@
       </c>
       <c r="C159" s="11"/>
     </row>
-    <row r="160" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A160" s="13" t="s">
         <v>473</v>
       </c>
@@ -4126,7 +4176,7 @@
       </c>
       <c r="C160" s="11"/>
     </row>
-    <row r="161" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A161" s="13" t="s">
         <v>475</v>
       </c>
@@ -4135,7 +4185,7 @@
       </c>
       <c r="C161" s="11"/>
     </row>
-    <row r="162" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A162" s="13" t="s">
         <v>477</v>
       </c>
@@ -4146,7 +4196,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A163" s="13" t="s">
         <v>479</v>
       </c>
@@ -4157,7 +4207,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A164" s="13" t="s">
         <v>481</v>
       </c>
@@ -4166,7 +4216,7 @@
       </c>
       <c r="C164" s="11"/>
     </row>
-    <row r="165" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A165" s="13" t="s">
         <v>483</v>
       </c>
@@ -4175,7 +4225,7 @@
       </c>
       <c r="C165" s="11"/>
     </row>
-    <row r="166" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A166" s="13" t="s">
         <v>485</v>
       </c>
@@ -4184,7 +4234,7 @@
       </c>
       <c r="C166" s="11"/>
     </row>
-    <row r="167" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A167" s="13" t="s">
         <v>487</v>
       </c>
@@ -4193,7 +4243,7 @@
       </c>
       <c r="C167" s="11"/>
     </row>
-    <row r="168" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A168" s="13" t="s">
         <v>489</v>
       </c>
@@ -4202,7 +4252,7 @@
       </c>
       <c r="C168" s="11"/>
     </row>
-    <row r="169" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A169" s="13" t="s">
         <v>491</v>
       </c>
@@ -4211,7 +4261,7 @@
       </c>
       <c r="C169" s="11"/>
     </row>
-    <row r="170" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A170" s="13" t="s">
         <v>493</v>
       </c>
@@ -4220,7 +4270,7 @@
       </c>
       <c r="C170" s="11"/>
     </row>
-    <row r="171" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A171" s="13" t="s">
         <v>495</v>
       </c>
@@ -4231,7 +4281,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A172" s="13" t="s">
         <v>496</v>
       </c>
@@ -4242,7 +4292,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A173" s="13" t="s">
         <v>498</v>
       </c>
@@ -4253,7 +4303,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A174" s="13" t="s">
         <v>500</v>
       </c>
@@ -4264,7 +4314,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A175" s="13" t="s">
         <v>502</v>
       </c>
@@ -4275,7 +4325,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A176" s="13" t="s">
         <v>504</v>
       </c>
@@ -4284,7 +4334,7 @@
       </c>
       <c r="C176" s="11"/>
     </row>
-    <row r="177" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A177" s="13" t="s">
         <v>506</v>
       </c>
@@ -4295,7 +4345,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A178" s="13" t="s">
         <v>508</v>
       </c>
@@ -4306,7 +4356,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A179" s="13" t="s">
         <v>513</v>
       </c>
@@ -4318,12 +4368,12 @@
   </sheetData>
   <autoFilter ref="A1:C3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A3">
-    <cfRule type="containsBlanks" dxfId="20" priority="121" stopIfTrue="1">
+    <cfRule type="containsBlanks" dxfId="17" priority="121" stopIfTrue="1">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B178">
-    <cfRule type="duplicateValues" dxfId="19" priority="122" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="122" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="74" fitToHeight="7" orientation="portrait" r:id="rId1"/>
@@ -4332,732 +4382,1742 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y33"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="32.85546875" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" customWidth="1"/>
-    <col min="5" max="7" width="43.42578125" customWidth="1"/>
-    <col min="17" max="17" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24.5703125" customWidth="1"/>
-    <col min="25" max="25" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="32.88671875" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="4" max="4" width="23.109375" customWidth="1"/>
+    <col min="5" max="5" width="43.44140625" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" customWidth="1"/>
+    <col min="14" max="16" width="9.109375" style="23"/>
+    <col min="17" max="17" width="11.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="9.109375" style="23"/>
+    <col min="21" max="21" width="24.5546875" style="23" customWidth="1"/>
+    <col min="22" max="24" width="9.109375" style="23"/>
+    <col min="25" max="25" width="11.44140625" style="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>608</v>
+        <v>579</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>520</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>521</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="H1" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="H1" s="22" t="s">
         <v>522</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="22" t="s">
         <v>522</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="22" t="s">
         <v>522</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="22" t="s">
         <v>522</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="207" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
-        <v>593</v>
-      </c>
-      <c r="B2" s="24">
+    <row r="2" spans="1:25" ht="145.19999999999999" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B2" s="20">
         <v>5</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>557</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>558</v>
-      </c>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="D2" s="27" t="s">
+        <v>553</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>613</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
       <c r="H2" t="s">
-        <v>406</v>
-      </c>
-      <c r="N2" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A2,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Zavazadla&lt;/displayName&gt;</v>
-      </c>
-      <c r="O2" t="str">
-        <f>CONCATENATE("&lt;",B$1,"&gt;",B2,"&lt;/",B$1,"&gt;")</f>
+        <v>586</v>
+      </c>
+      <c r="I2" t="s">
+        <v>449</v>
+      </c>
+      <c r="N2" s="23" t="str">
+        <f t="shared" ref="N2:N13" si="0">CONCATENATE("&lt;",A$1,"&gt;",A2,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Nepokládejte zavazadla na sedadla. &lt;/displayName&gt;</v>
+      </c>
+      <c r="O2" s="23" t="str">
+        <f t="shared" ref="O2:O13" si="1">CONCATENATE("&lt;",B$1,"&gt;",B2,"&lt;/",B$1,"&gt;")</f>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P2" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C2,"&lt;/",C$1,"&gt;")</f>
+      <c r="P2" s="23" t="str">
+        <f t="shared" ref="P2:P13" si="2">CONCATENATE("&lt;",C$1,"&gt;",C2,"&lt;/",C$1,"&gt;")</f>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q2" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D2,"&lt;/",D$1,"&gt;")</f>
+      <c r="Q2" s="23" t="str">
+        <f t="shared" ref="Q2:Q13" si="3">CONCATENATE("&lt;",D$1,"&gt;",D2,"&lt;/",D$1,"&gt;")</f>
         <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Luggage&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
       </c>
-      <c r="R2" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E2,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že pokládat
-zavazadla na sedadla není dovoleno.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+      <c r="R2" s="23" t="str">
+        <f t="shared" ref="R2:R13" si="4">CONCATENATE("&lt;",E$1,"&gt;",E2,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Nepokládejte zavazadla na sedadla.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
       </c>
-      <c r="S2" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F2,"&lt;/",F$1,"&gt;")</f>
+      <c r="S2" s="23" t="str">
+        <f t="shared" ref="S2:S13" si="5">CONCATENATE("&lt;",F$1,"&gt;",F2,"&lt;/",F$1,"&gt;")</f>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T2" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G2,"&lt;/",G$1,"&gt;")</f>
+      <c r="T2" s="23" t="str">
+        <f t="shared" ref="T2:T13" si="6">CONCATENATE("&lt;",G$1,"&gt;",G2,"&lt;/",G$1,"&gt;")</f>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U2" t="str">
-        <f>IF(H2&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H2,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v>&lt;mp3&gt;H239.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V2" t="str">
-        <f>IF(I2&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I2,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="U2" s="23" t="str">
+        <f t="shared" ref="U2:U13" si="7">IF(H2&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H2,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V2" s="23" t="str">
+        <f t="shared" ref="V2:V13" si="8">IF(I2&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I2,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H339.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W2" s="23" t="str">
+        <f t="shared" ref="W2:W13" si="9">IF(J2&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J2,".mp3","&lt;/",J$1,"&gt;"),"")</f>
         <v/>
       </c>
-      <c r="W2" t="str">
-        <f>IF(J2&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J2,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="X2" s="23" t="str">
+        <f t="shared" ref="X2:X13" si="10">IF(K2&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K2,".mp3","&lt;/",K$1,"&gt;"),"")</f>
         <v/>
       </c>
-      <c r="X2" t="str">
-        <f>IF(K2&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K2,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <f>CONCATENATE("&lt;announcement&gt;",N2,O2,P2,Q2,R2,S2,T2,U2,V2,W2,X2,"&lt;/announcement&gt;")</f>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Zavazadla&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Luggage&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že pokládat
-zavazadla na sedadla není dovoleno.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H239.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" ht="207" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
-        <v>592</v>
-      </c>
-      <c r="B3" s="24">
+      <c r="Y2" s="23" t="str">
+        <f t="shared" ref="Y2:Y13" si="11">CONCATENATE("&lt;announcement&gt;",N2,O2,P2,Q2,R2,S2,T2,U2,V2,W2,X2,"&lt;/announcement&gt;")</f>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Nepokládejte zavazadla na sedadla. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Luggage&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Nepokládejte zavazadla na sedadla.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H339.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="118.8" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B3" s="20">
         <v>5</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>555</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="D3" s="27" t="s">
+        <v>552</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>619</v>
+      </c>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
       <c r="H3" t="s">
+        <v>586</v>
+      </c>
+      <c r="I3" t="s">
         <v>451</v>
       </c>
-      <c r="N3" t="str">
-        <f t="shared" ref="N3:N8" si="0">CONCATENATE("&lt;",A$1,"&gt;",A3,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Zákaz jídla a pití &lt;/displayName&gt;</v>
-      </c>
-      <c r="O3" t="str">
-        <f t="shared" ref="O3:O26" si="1">CONCATENATE("&lt;",B$1,"&gt;",B3,"&lt;/",B$1,"&gt;")</f>
-        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
-      </c>
-      <c r="P3" t="str">
-        <f t="shared" ref="P3:P8" si="2">CONCATENATE("&lt;",C$1,"&gt;",C3,"&lt;/",C$1,"&gt;")</f>
-        <v>&lt;type&gt;&lt;/type&gt;</v>
-      </c>
-      <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q8" si="3">CONCATENATE("&lt;",D$1,"&gt;",D3,"&lt;/",D$1,"&gt;")</f>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R3" t="str">
-        <f t="shared" ref="R3:R8" si="4">CONCATENATE("&lt;",E$1,"&gt;",E3,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že konzumace
-potravin není ve vozidlech povolena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not eat any food in the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="S3" t="str">
-        <f t="shared" ref="S3:S8" si="5">CONCATENATE("&lt;",F$1,"&gt;",F3,"&lt;/",F$1,"&gt;")</f>
-        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="T3" t="str">
-        <f t="shared" ref="T3:T8" si="6">CONCATENATE("&lt;",G$1,"&gt;",G3,"&lt;/",G$1,"&gt;")</f>
-        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
-      </c>
-      <c r="U3" t="str">
-        <f t="shared" ref="U3:U8" si="7">IF(H3&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H3,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v>&lt;mp3&gt;H340.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V3" t="str">
-        <f>IF(I3&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I3,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W3" t="str">
-        <f>IF(J3&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J3,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="X3" t="str">
-        <f>IF(K3&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K3,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y3" t="str">
-        <f t="shared" ref="Y3:Y26" si="8">CONCATENATE("&lt;announcement&gt;",N3,O3,P3,Q3,R3,S3,T3,U3,V3,W3,X3,"&lt;/announcement&gt;")</f>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Zákaz jídla a pití &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že konzumace
-potravin není ve vozidlech povolena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not eat any food in the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H340.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="207" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>591</v>
-      </c>
-      <c r="B4" s="24">
-        <v>5</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>562</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>563</v>
-      </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" t="s">
-        <v>408</v>
-      </c>
-      <c r="N4" t="str">
+      <c r="J3" t="s">
+        <v>595</v>
+      </c>
+      <c r="K3" t="s">
+        <v>596</v>
+      </c>
+      <c r="N3" s="23" t="str">
         <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Kočárek&lt;/displayName&gt;</v>
-      </c>
-      <c r="O4" t="str">
+        <v>&lt;displayName&gt;Zákaz konzumace potravin ve voze. &lt;/displayName&gt;</v>
+      </c>
+      <c r="O3" s="23" t="str">
         <f t="shared" si="1"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P4" t="str">
+      <c r="P3" s="23" t="str">
         <f t="shared" si="2"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="Q3" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R3" s="23" t="str">
+        <f t="shared" si="4"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Konzumace potravin ve voze není povolena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not eat in the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S3" s="23" t="str">
+        <f t="shared" si="5"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T3" s="23" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U3" s="23" t="str">
+        <f t="shared" si="7"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V3" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;mp3&gt;H340.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W3" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>&lt;mp3&gt;H740.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="X3" s="23" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;mp3&gt;H741.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="Y3" s="23" t="str">
+        <f t="shared" si="11"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Zákaz konzumace potravin ve voze. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Konzumace potravin ve voze není povolena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not eat in the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H340.mp3&lt;/mp3&gt;&lt;mp3&gt;H740.mp3&lt;/mp3&gt;&lt;mp3&gt;H741.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="121.2" x14ac:dyDescent="0.45">
+      <c r="A4" s="29" t="s">
+        <v>603</v>
+      </c>
+      <c r="B4" s="30">
+        <v>5</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="32" t="s">
+        <v>556</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>583</v>
+      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" t="s">
+        <v>586</v>
+      </c>
+      <c r="I4" t="s">
+        <v>408</v>
+      </c>
+      <c r="N4" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;displayName&gt;Uvolněte prostor pro kočárek. &lt;/displayName&gt;</v>
+      </c>
+      <c r="O4" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P4" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q4" s="23" t="str">
         <f t="shared" si="3"/>
         <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pram&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
       </c>
-      <c r="R4" t="str">
+      <c r="R4" s="23" t="str">
         <f t="shared" si="4"/>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
-místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="S4" t="str">
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,&amp;lt;br&amp;gt;místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please make room for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S4" s="23" t="str">
         <f t="shared" si="5"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T4" t="str">
+      <c r="T4" s="23" t="str">
         <f t="shared" si="6"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U4" t="str">
+      <c r="U4" s="23" t="str">
         <f t="shared" si="7"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V4" s="23" t="str">
+        <f t="shared" si="8"/>
         <v>&lt;mp3&gt;H240.mp3&lt;/mp3&gt;</v>
       </c>
-      <c r="V4" t="str">
-        <f>IF(I4&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I4,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="W4" s="23" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="W4" t="str">
-        <f>IF(J4&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J4,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="X4" s="23" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="X4" t="str">
-        <f>IF(K4&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K4,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y4" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Kočárek&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pram&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
-místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H240.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="207" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
-        <v>590</v>
-      </c>
-      <c r="B5" s="24">
+      <c r="Y4" s="23" t="str">
+        <f t="shared" si="11"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Uvolněte prostor pro kočárek. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pram&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,&amp;lt;br&amp;gt;místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please make room for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H240.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="134.4" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="B5" s="20">
         <v>5</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>560</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>561</v>
-      </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
+      <c r="D5" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>584</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
       <c r="H5" t="s">
+        <v>586</v>
+      </c>
+      <c r="I5" t="s">
         <v>415</v>
       </c>
-      <c r="N5" t="str">
+      <c r="N5" s="23" t="str">
         <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Invalidní vozík&lt;/displayName&gt;</v>
-      </c>
-      <c r="O5" t="str">
+        <v>&lt;displayName&gt;Uvolněte prostor pro invalidní vozík. &lt;/displayName&gt;</v>
+      </c>
+      <c r="O5" s="23" t="str">
         <f t="shared" si="1"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P5" t="str">
+      <c r="P5" s="23" t="str">
         <f t="shared" si="2"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="Q5" s="23" t="str">
         <f t="shared" si="3"/>
         <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_WheelChair&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
       </c>
-      <c r="R5" t="str">
+      <c r="R5" s="23" t="str">
         <f t="shared" si="4"/>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
-místo pro invalidní vozík.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a wheelchair.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="S5" t="str">
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,&amp;lt;br&amp;gt;prostor pro invalidní vozík.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please make room for a wheelchair.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S5" s="23" t="str">
         <f t="shared" si="5"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T5" t="str">
+      <c r="T5" s="23" t="str">
         <f t="shared" si="6"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U5" t="str">
+      <c r="U5" s="23" t="str">
         <f t="shared" si="7"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V5" s="23" t="str">
+        <f t="shared" si="8"/>
         <v>&lt;mp3&gt;H260.mp3&lt;/mp3&gt;</v>
       </c>
-      <c r="V5" t="str">
-        <f>IF(I5&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I5,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="W5" s="23" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="W5" t="str">
-        <f>IF(J5&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J5,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="X5" s="23" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="X5" t="str">
-        <f>IF(K5&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K5,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y5" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Invalidní vozík&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_WheelChair&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
-místo pro invalidní vozík.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a wheelchair.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H260.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="224.25" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
-        <v>589</v>
-      </c>
-      <c r="B6" s="24">
+      <c r="Y5" s="23" t="str">
+        <f t="shared" si="11"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Uvolněte prostor pro invalidní vozík. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_WheelChair&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,&amp;lt;br&amp;gt;prostor pro invalidní vozík.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please make room for a wheelchair.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H260.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="121.2" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="B6" s="20">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
+      <c r="D6" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>614</v>
+      </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
       <c r="H6" t="s">
-        <v>309</v>
-      </c>
-      <c r="N6" t="str">
+        <v>586</v>
+      </c>
+      <c r="I6" t="s">
+        <v>350</v>
+      </c>
+      <c r="N6" s="23" t="str">
         <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Postupujte dále do vozu&lt;/displayName&gt;</v>
-      </c>
-      <c r="O6" t="str">
+        <v>&lt;displayName&gt;Uvolněte přední dveře, postupte dále do vozu. &lt;/displayName&gt;</v>
+      </c>
+      <c r="O6" s="23" t="str">
         <f t="shared" si="1"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P6" t="str">
+      <c r="P6" s="23" t="str">
         <f t="shared" si="2"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="Q6" s="23" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_GoFurther&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R6" t="str">
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R6" s="23" t="str">
         <f t="shared" si="4"/>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,
-          postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-          &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further
-          into the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="S6" t="str">
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,&amp;lt;br&amp;gt;postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further inside the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S6" s="23" t="str">
         <f t="shared" si="5"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T6" t="str">
+      <c r="T6" s="23" t="str">
         <f t="shared" si="6"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U6" t="str">
+      <c r="U6" s="23" t="str">
         <f t="shared" si="7"/>
-        <v>&lt;mp3&gt;H179.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V6" t="str">
-        <f>IF(I6&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I6,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V6" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;mp3&gt;H206.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W6" s="23" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="W6" t="str">
-        <f>IF(J6&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J6,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="X6" s="23" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="X6" t="str">
-        <f>IF(K6&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K6,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y6" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Postupujte dále do vozu&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_GoFurther&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,
-          postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-          &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further
-          into the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H179.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="189.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
-        <v>595</v>
-      </c>
-      <c r="B7" s="24">
+      <c r="Y6" s="23" t="str">
+        <f t="shared" si="11"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Uvolněte přední dveře, postupte dále do vozu. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,&amp;lt;br&amp;gt;postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further inside the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H206.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="108" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="B7" s="20">
         <v>5</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>567</v>
-      </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
+      <c r="D7" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>585</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
       <c r="H7" t="s">
+        <v>586</v>
+      </c>
+      <c r="I7" t="s">
         <v>423</v>
       </c>
-      <c r="N7" t="str">
+      <c r="J7" t="s">
+        <v>277</v>
+      </c>
+      <c r="N7" s="23" t="str">
         <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Vyčkávání na čas odjezdu&lt;/displayName&gt;</v>
-      </c>
-      <c r="O7" t="str">
+        <v>&lt;displayName&gt;Vyčkáváme na odjezd dle jízdního řádu. &lt;/displayName&gt;</v>
+      </c>
+      <c r="O7" s="23" t="str">
         <f t="shared" si="1"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P7" t="str">
+      <c r="P7" s="23" t="str">
         <f t="shared" si="2"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="Q7" s="23" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R7" t="str">
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R7" s="23" t="str">
         <f t="shared" si="4"/>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu
-dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled
-departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="S7" t="str">
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S7" s="23" t="str">
         <f t="shared" si="5"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T7" t="str">
+      <c r="T7" s="23" t="str">
         <f t="shared" si="6"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U7" t="str">
+      <c r="U7" s="23" t="str">
         <f t="shared" si="7"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V7" s="23" t="str">
+        <f t="shared" si="8"/>
         <v>&lt;mp3&gt;H281.mp3&lt;/mp3&gt;</v>
       </c>
-      <c r="V7" t="str">
-        <f>IF(I7&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I7,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="W7" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>&lt;mp3&gt;H160.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="X7" s="23" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="W7" t="str">
-        <f>IF(J7&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J7,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="X7" t="str">
-        <f>IF(K7&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K7,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y7" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Vyčkávání na čas odjezdu&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu
-dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled
-departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H281.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="155.25" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
-        <v>594</v>
-      </c>
-      <c r="B8" s="24">
+      <c r="Y7" s="23" t="str">
+        <f t="shared" si="11"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Vyčkáváme na odjezd dle jízdního řádu. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H281.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="108" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B8" s="20">
         <v>5</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>596</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
+      <c r="D8" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>615</v>
+      </c>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
       <c r="H8" t="s">
-        <v>428</v>
-      </c>
-      <c r="N8" t="str">
+        <v>586</v>
+      </c>
+      <c r="I8" t="s">
+        <v>352</v>
+      </c>
+      <c r="J8" t="s">
+        <v>277</v>
+      </c>
+      <c r="N8" s="23" t="str">
         <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Vzájemný přestup&lt;/displayName&gt;</v>
-      </c>
-      <c r="O8" t="str">
+        <v>&lt;displayName&gt;Přepravní kontrola, připravte si cestovní doklady. &lt;/displayName&gt;</v>
+      </c>
+      <c r="O8" s="23" t="str">
         <f t="shared" si="1"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P8" t="str">
+      <c r="P8" s="23" t="str">
         <f t="shared" si="2"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="Q8" s="23" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Bus&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R8" t="str">
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R8" s="23" t="str">
         <f t="shared" si="4"/>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for a mutual transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="S8" t="str">
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Přepravní kontrola, prosíme, připravte si cestovní doklady.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Ticket inspection. Please have your tickets ready.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S8" s="23" t="str">
         <f t="shared" si="5"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T8" t="str">
+      <c r="T8" s="23" t="str">
         <f t="shared" si="6"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U8" t="str">
+      <c r="U8" s="23" t="str">
         <f t="shared" si="7"/>
-        <v>&lt;mp3&gt;H284.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V8" t="str">
-        <f>IF(I8&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I8,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V8" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;mp3&gt;H207.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W8" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>&lt;mp3&gt;H160.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="X8" s="23" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="W8" t="str">
-        <f>IF(J8&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J8,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="X8" t="str">
-        <f>IF(K8&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K8,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y8" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Vzájemný přestup&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Bus&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for a mutual transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H284.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="172.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
-        <v>599</v>
-      </c>
-      <c r="B9" s="24">
+      <c r="Y8" s="23" t="str">
+        <f t="shared" si="11"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Přepravní kontrola, připravte si cestovní doklady. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Přepravní kontrola, prosíme, připravte si cestovní doklady.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Ticket inspection. Please have your tickets ready.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H207.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="108" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="B9" s="20">
         <v>5</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>598</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>597</v>
-      </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="N9" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A9,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Vzájemný přestup (vlak)&lt;/displayName&gt;</v>
-      </c>
-      <c r="O9" t="str">
+      <c r="D9" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>615</v>
+      </c>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" t="s">
+        <v>586</v>
+      </c>
+      <c r="I9" t="s">
+        <v>352</v>
+      </c>
+      <c r="J9" t="s">
+        <v>354</v>
+      </c>
+      <c r="N9" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;displayName&gt;Přepravní kontrola, výstup pouze předními dveřmi. &lt;/displayName&gt;</v>
+      </c>
+      <c r="O9" s="23" t="str">
         <f t="shared" si="1"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P9" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C9,"&lt;/",C$1,"&gt;")</f>
+      <c r="P9" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q9" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D9,"&lt;/",D$1,"&gt;")</f>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_SBahn&amp;quot;&amp;gt;~&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R9" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E9,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přestup z vlakové linky S dle stanovené čekací doby.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for an „S“ train transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="S9" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F9,"&lt;/",F$1,"&gt;")</f>
+      <c r="Q9" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R9" s="23" t="str">
+        <f t="shared" si="4"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Přepravní kontrola, prosíme, připravte si cestovní doklady.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Ticket inspection. Please have your tickets ready.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S9" s="23" t="str">
+        <f t="shared" si="5"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T9" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G9,"&lt;/",G$1,"&gt;")</f>
+      <c r="T9" s="23" t="str">
+        <f t="shared" si="6"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U9" t="str">
-        <f>IF(H9&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H9,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+      <c r="U9" s="23" t="str">
+        <f t="shared" si="7"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V9" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;mp3&gt;H207.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W9" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>&lt;mp3&gt;H208.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="X9" s="23" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V9" t="str">
-        <f>IF(I9&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I9,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W9" t="str">
-        <f>IF(J9&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J9,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="X9" t="str">
-        <f>IF(K9&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K9,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y9" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Vzájemný přestup (vlak)&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_SBahn&amp;quot;&amp;gt;~&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přestup z vlakové linky S dle stanovené čekací doby.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for an „S“ train transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="167.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
-        <v>603</v>
-      </c>
-      <c r="B10" s="24">
+      <c r="Y9" s="23" t="str">
+        <f t="shared" si="11"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Přepravní kontrola, výstup pouze předními dveřmi. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Přepravní kontrola, prosíme, připravte si cestovní doklady.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Ticket inspection. Please have your tickets ready.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H207.mp3&lt;/mp3&gt;&lt;mp3&gt;H208.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="121.2" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="B10" s="20">
         <v>5</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>609</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>565</v>
-      </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
+      <c r="D10" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>620</v>
+      </c>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
       <c r="H10" t="s">
-        <v>419</v>
-      </c>
-      <c r="N10" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A10,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Odklon&lt;/displayName&gt;</v>
-      </c>
-      <c r="O10" t="str">
+        <v>586</v>
+      </c>
+      <c r="I10" t="s">
+        <v>597</v>
+      </c>
+      <c r="N10" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;displayName&gt;Kočárek přepravujte na určeném místě. &lt;/displayName&gt;</v>
+      </c>
+      <c r="O10" s="23" t="str">
         <f t="shared" si="1"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P10" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C10,"&lt;/",C$1,"&gt;")</f>
+      <c r="P10" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q10" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D10,"&lt;/",D$1,"&gt;")</f>
-        <v>&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R10" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E10,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
-&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu silné automobilové dopravy
-pojede tato linka odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;This line will be rerouted due to heavy traffic.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
-&amp;lt;/color&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="S10" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F10,"&lt;/",F$1,"&gt;")</f>
+      <c r="Q10" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R10" s="23" t="str">
+        <f t="shared" si="4"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Kočárek přepravujte&amp;lt;br&amp;gt;na určeném místě.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please keep prams in the designated area.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S10" s="23" t="str">
+        <f t="shared" si="5"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T10" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G10,"&lt;/",G$1,"&gt;")</f>
+      <c r="T10" s="23" t="str">
+        <f t="shared" si="6"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U10" t="str">
-        <f>IF(H10&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H10,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v>&lt;mp3&gt;H279.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V10" t="str">
-        <f>IF(I10&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I10,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="U10" s="23" t="str">
+        <f t="shared" si="7"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V10" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;mp3&gt;H267.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W10" s="23" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="W10" t="str">
-        <f>IF(J10&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J10,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="X10" s="23" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="X10" t="str">
-        <f>IF(K10&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K10,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y10" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Odklon&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
-&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu silné automobilové dopravy
-pojede tato linka odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;This line will be rerouted due to heavy traffic.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
-&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H279.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
-        <v>600</v>
-      </c>
-      <c r="B11" s="24">
+      <c r="Y10" s="23" t="str">
+        <f t="shared" si="11"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Kočárek přepravujte na určeném místě. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Kočárek přepravujte&amp;lt;br&amp;gt;na určeném místě.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please keep prams in the designated area.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H267.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="121.2" x14ac:dyDescent="0.45">
+      <c r="A11" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B11" s="20">
         <v>5</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>602</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>601</v>
-      </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="N11" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A11,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Letiště DEMO&lt;/displayName&gt;</v>
-      </c>
-      <c r="O11" t="str">
+      <c r="D11" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>616</v>
+      </c>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" t="s">
+        <v>586</v>
+      </c>
+      <c r="I11" t="s">
+        <v>598</v>
+      </c>
+      <c r="N11" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;displayName&gt;Pes musí být opatřen náhubkem a vodítkem.&lt;/displayName&gt;</v>
+      </c>
+      <c r="O11" s="23" t="str">
         <f t="shared" si="1"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P11" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C11,"&lt;/",C$1,"&gt;")</f>
+      <c r="P11" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q11" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D11,"&lt;/",D$1,"&gt;")</f>
+      <c r="Q11" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R11" s="23" t="str">
+        <f t="shared" si="4"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Pes musí být opatřen náhubkem a vodítkem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Dogs must be kept on a leash and wear a muzzle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S11" s="23" t="str">
+        <f t="shared" si="5"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T11" s="23" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U11" s="23" t="str">
+        <f t="shared" si="7"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V11" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;mp3&gt;H433.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W11" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="X11" s="23" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="Y11" s="23" t="str">
+        <f t="shared" si="11"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Pes musí být opatřen náhubkem a vodítkem.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Pes musí být opatřen náhubkem a vodítkem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Dogs must be kept on a leash and wear a muzzle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H433.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="147.6" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="B12" s="20">
+        <v>5</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>627</v>
+      </c>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" t="s">
+        <v>586</v>
+      </c>
+      <c r="I12" t="s">
+        <v>453</v>
+      </c>
+      <c r="N12" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;displayName&gt;Klimatizace v provozu, neotevírejte okna.&lt;/displayName&gt;</v>
+      </c>
+      <c r="O12" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P12" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q12" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R12" s="23" t="str">
+        <f t="shared" si="4"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Klimatizace v provozu, prosíme,&amp;lt;br&amp;gt; neotevírejte okna.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Air conditioning is operating.&amp;lt;br&amp;gt;Please do not open the windows.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S12" s="23" t="str">
+        <f t="shared" si="5"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T12" s="23" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U12" s="23" t="str">
+        <f t="shared" si="7"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V12" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;mp3&gt;H350.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W12" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="X12" s="23" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="Y12" s="23" t="str">
+        <f t="shared" si="11"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Klimatizace v provozu, neotevírejte okna.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Klimatizace v provozu, prosíme,&amp;lt;br&amp;gt; neotevírejte okna.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Air conditioning is operating.&amp;lt;br&amp;gt;Please do not open the windows.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H350.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="174" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="B13" s="20">
+        <v>5</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>580</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>621</v>
+      </c>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" t="s">
+        <v>586</v>
+      </c>
+      <c r="I13" t="s">
+        <v>599</v>
+      </c>
+      <c r="J13" t="s">
+        <v>277</v>
+      </c>
+      <c r="N13" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;displayName&gt;Porucha, vůz dále nepokračuje. &lt;/displayName&gt;</v>
+      </c>
+      <c r="O13" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P13" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q13" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R13" s="23" t="str">
+        <f t="shared" si="4"/>
+        <v>&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu technické závady vůz dále nepokračuje.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to a technical failure, this vehicle will not continue its journey.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S13" s="23" t="str">
+        <f t="shared" si="5"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T13" s="23" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U13" s="23" t="str">
+        <f t="shared" si="7"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V13" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;mp3&gt;H148.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W13" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>&lt;mp3&gt;H160.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="X13" s="23" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="Y13" s="23" t="str">
+        <f t="shared" si="11"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Porucha, vůz dále nepokračuje. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu technické závady vůz dále nepokračuje.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to a technical failure, this vehicle will not continue its journey.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H148.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="213.6" x14ac:dyDescent="0.45">
+      <c r="A14" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="B14" s="20">
+        <v>5</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>580</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>622</v>
+      </c>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" t="s">
+        <v>586</v>
+      </c>
+      <c r="I14" t="s">
+        <v>326</v>
+      </c>
+      <c r="J14" t="s">
+        <v>277</v>
+      </c>
+      <c r="N14" s="23" t="str">
+        <f t="shared" ref="N14:N33" si="12">CONCATENATE("&lt;",A$1,"&gt;",A14,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Porucha, přestupte do náhradního vozu. &lt;/displayName&gt;</v>
+      </c>
+      <c r="O14" s="23" t="str">
+        <f t="shared" ref="O14:O33" si="13">CONCATENATE("&lt;",B$1,"&gt;",B14,"&lt;/",B$1,"&gt;")</f>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P14" s="23" t="str">
+        <f t="shared" ref="P14:P33" si="14">CONCATENATE("&lt;",C$1,"&gt;",C14,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q14" s="23" t="str">
+        <f t="shared" ref="Q14:Q33" si="15">CONCATENATE("&lt;",D$1,"&gt;",D14,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R14" s="23" t="str">
+        <f t="shared" ref="R14:R33" si="16">CONCATENATE("&lt;",E$1,"&gt;",E14,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
+&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu technické závady vůz dále nepokračuje. Prosíme, přestupte do náhradního vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to a technical failure, this vehicle will not continue its journey. Please transfer to a replacement vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S14" s="23" t="str">
+        <f t="shared" ref="S14:S33" si="17">CONCATENATE("&lt;",F$1,"&gt;",F14,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T14" s="23" t="str">
+        <f t="shared" ref="T14:T33" si="18">CONCATENATE("&lt;",G$1,"&gt;",G14,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U14" s="23" t="str">
+        <f t="shared" ref="U14:U33" si="19">IF(H14&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H14,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V14" s="23" t="str">
+        <f t="shared" ref="V14:V33" si="20">IF(I14&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I14,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H188.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W14" s="23" t="str">
+        <f t="shared" ref="W14:W33" si="21">IF(J14&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J14,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H160.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="X14" s="23" t="str">
+        <f t="shared" ref="X14:X33" si="22">IF(K14&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K14,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y14" s="23" t="str">
+        <f t="shared" ref="Y14:Y33" si="23">CONCATENATE("&lt;announcement&gt;",N14,O14,P14,Q14,R14,S14,T14,U14,V14,W14,X14,"&lt;/announcement&gt;")</f>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Porucha, přestupte do náhradního vozu. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
+&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu technické závady vůz dále nepokračuje. Prosíme, přestupte do náhradního vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to a technical failure, this vehicle will not continue its journey. Please transfer to a replacement vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H188.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="187.2" x14ac:dyDescent="0.45">
+      <c r="A15" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B15" s="20">
+        <v>5</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>580</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>624</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" t="s">
+        <v>586</v>
+      </c>
+      <c r="I15" t="s">
+        <v>197</v>
+      </c>
+      <c r="J15" t="s">
+        <v>283</v>
+      </c>
+      <c r="K15" t="s">
+        <v>277</v>
+      </c>
+      <c r="N15" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;Linka je zde ukončena, neprůjezdnost trasy.&lt;/displayName&gt;</v>
+      </c>
+      <c r="O15" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P15" s="23" t="str">
+        <f t="shared" si="14"/>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q15" s="23" t="str">
+        <f t="shared" si="15"/>
+        <v>&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R15" s="23" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu neprůjezdnosti trasy je linka vedena odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to an obstruction on the route, this line is diverted.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S15" s="23" t="str">
+        <f t="shared" si="17"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T15" s="23" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U15" s="23" t="str">
+        <f t="shared" si="19"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V15" s="23" t="str">
+        <f t="shared" si="20"/>
+        <v>&lt;mp3&gt;H115.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W15" s="23" t="str">
+        <f t="shared" si="21"/>
+        <v>&lt;mp3&gt;H163.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="X15" s="23" t="str">
+        <f t="shared" si="22"/>
+        <v>&lt;mp3&gt;H160.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="Y15" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Linka je zde ukončena, neprůjezdnost trasy.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu neprůjezdnosti trasy je linka vedena odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to an obstruction on the route, this line is diverted.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H115.mp3&lt;/mp3&gt;&lt;mp3&gt;H163.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="174" x14ac:dyDescent="0.45">
+      <c r="A16" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="B16" s="20">
+        <v>5</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>580</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>623</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" t="s">
+        <v>586</v>
+      </c>
+      <c r="I16" t="s">
+        <v>197</v>
+      </c>
+      <c r="J16" t="s">
+        <v>281</v>
+      </c>
+      <c r="K16" t="s">
+        <v>277</v>
+      </c>
+      <c r="N16" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;Linka je zkrácena, neprůjezdnost trasy.&lt;/displayName&gt;</v>
+      </c>
+      <c r="O16" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P16" s="23" t="str">
+        <f t="shared" si="14"/>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q16" s="23" t="str">
+        <f t="shared" si="15"/>
+        <v>&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R16" s="23" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu neprůjezdnosti trasy je linka dočasně zkrácena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to an obstruction on the route, this line is shortened.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S16" s="23" t="str">
+        <f t="shared" si="17"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T16" s="23" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U16" s="23" t="str">
+        <f t="shared" si="19"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V16" s="23" t="str">
+        <f t="shared" si="20"/>
+        <v>&lt;mp3&gt;H115.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W16" s="23" t="str">
+        <f t="shared" si="21"/>
+        <v>&lt;mp3&gt;H162.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="X16" s="23" t="str">
+        <f t="shared" si="22"/>
+        <v>&lt;mp3&gt;H160.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="Y16" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Linka je zkrácena, neprůjezdnost trasy.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu neprůjezdnosti trasy je linka dočasně zkrácena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to an obstruction on the route, this line is shortened.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H115.mp3&lt;/mp3&gt;&lt;mp3&gt;H162.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="160.80000000000001" x14ac:dyDescent="0.45">
+      <c r="A17" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="B17" s="20">
+        <v>5</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>592</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" t="s">
+        <v>586</v>
+      </c>
+      <c r="I17" t="s">
+        <v>600</v>
+      </c>
+      <c r="N17" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;Provoz metra přerušen, použijte náhradní dopravu.&lt;/displayName&gt;</v>
+      </c>
+      <c r="O17" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P17" s="23" t="str">
+        <f t="shared" si="14"/>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q17" s="23" t="str">
+        <f t="shared" si="15"/>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R17" s="23" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Provoz metra je přerušen, &amp;lt;br&amp;gt;použijte prosím linky povrchové 
+a náhradní dopravy.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Metro service is suspended.&amp;lt;br&amp;gt;Please use surface transport and replacement lines.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S17" s="23" t="str">
+        <f t="shared" si="17"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T17" s="23" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U17" s="23" t="str">
+        <f t="shared" si="19"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V17" s="23" t="str">
+        <f t="shared" si="20"/>
+        <v>&lt;mp3&gt;H504.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W17" s="23" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="X17" s="23" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="Y17" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Provoz metra přerušen, použijte náhradní dopravu.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Provoz metra je přerušen, &amp;lt;br&amp;gt;použijte prosím linky povrchové 
+a náhradní dopravy.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Metro service is suspended.&amp;lt;br&amp;gt;Please use surface transport and replacement lines.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H504.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="147.6" x14ac:dyDescent="0.45">
+      <c r="A18" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="B18" s="20">
+        <v>5</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>618</v>
+      </c>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" t="s">
+        <v>586</v>
+      </c>
+      <c r="I18" t="s">
+        <v>601</v>
+      </c>
+      <c r="J18" t="s">
+        <v>277</v>
+      </c>
+      <c r="N18" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;Provoz tramvají přerušen, použijte náhradní dopravu.&lt;/displayName&gt;</v>
+      </c>
+      <c r="O18" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P18" s="23" t="str">
+        <f t="shared" si="14"/>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q18" s="23" t="str">
+        <f t="shared" si="15"/>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R18" s="23" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Provoz tramvají přerušen,&amp;lt;br&amp;gt;použijte prosím linky povrchové a náhradní dopravy.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Tram service is suspended. Please use other surface transport and replacement lines.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S18" s="23" t="str">
+        <f t="shared" si="17"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T18" s="23" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U18" s="23" t="str">
+        <f t="shared" si="19"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V18" s="23" t="str">
+        <f t="shared" si="20"/>
+        <v>&lt;mp3&gt;H923.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W18" s="23" t="str">
+        <f t="shared" si="21"/>
+        <v>&lt;mp3&gt;H160.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="X18" s="23" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="Y18" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Provoz tramvají přerušen, použijte náhradní dopravu.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Provoz tramvají přerušen,&amp;lt;br&amp;gt;použijte prosím linky povrchové a náhradní dopravy.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Tram service is suspended. Please use other surface transport and replacement lines.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H923.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="121.2" x14ac:dyDescent="0.45">
+      <c r="A19" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B19" s="20">
+        <v>5</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>617</v>
+      </c>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" t="s">
+        <v>586</v>
+      </c>
+      <c r="I19" t="s">
+        <v>428</v>
+      </c>
+      <c r="J19" t="s">
+        <v>277</v>
+      </c>
+      <c r="N19" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;Vyčkáváme na vzájemný přestup.&lt;/displayName&gt;</v>
+      </c>
+      <c r="O19" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P19" s="23" t="str">
+        <f t="shared" si="14"/>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q19" s="23" t="str">
+        <f t="shared" si="15"/>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R19" s="23" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for a connecting service.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S19" s="23" t="str">
+        <f t="shared" si="17"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T19" s="23" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U19" s="23" t="str">
+        <f t="shared" si="19"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V19" s="23" t="str">
+        <f t="shared" si="20"/>
+        <v>&lt;mp3&gt;H284.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W19" s="23" t="str">
+        <f t="shared" si="21"/>
+        <v>&lt;mp3&gt;H160.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="X19" s="23" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="Y19" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Vyčkáváme na vzájemný přestup.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for a connecting service.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H284.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="174" x14ac:dyDescent="0.45">
+      <c r="A20" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="B20" s="20">
+        <v>5</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>580</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>624</v>
+      </c>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" t="s">
+        <v>586</v>
+      </c>
+      <c r="I20" t="s">
+        <v>197</v>
+      </c>
+      <c r="J20" t="s">
+        <v>285</v>
+      </c>
+      <c r="K20" t="s">
+        <v>277</v>
+      </c>
+      <c r="N20" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;Linka jede odklonem, neprůjezdnost trasy.&lt;/displayName&gt;</v>
+      </c>
+      <c r="O20" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P20" s="23" t="str">
+        <f t="shared" si="14"/>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q20" s="23" t="str">
+        <f t="shared" si="15"/>
+        <v>&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R20" s="23" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu neprůjezdnosti trasy je linka vedena odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to an obstruction on the route, this line is diverted.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S20" s="23" t="str">
+        <f t="shared" si="17"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T20" s="23" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U20" s="23" t="str">
+        <f t="shared" si="19"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V20" s="23" t="str">
+        <f t="shared" si="20"/>
+        <v>&lt;mp3&gt;H115.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W20" s="23" t="str">
+        <f t="shared" si="21"/>
+        <v>&lt;mp3&gt;H164.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="X20" s="23" t="str">
+        <f t="shared" si="22"/>
+        <v>&lt;mp3&gt;H160.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="Y20" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Linka jede odklonem, neprůjezdnost trasy.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu neprůjezdnosti trasy je linka vedena odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to an obstruction on the route, this line is diverted.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H115.mp3&lt;/mp3&gt;&lt;mp3&gt;H164.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="134.4" x14ac:dyDescent="0.45">
+      <c r="A21" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B21" s="20">
+        <v>5</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>628</v>
+      </c>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" t="s">
+        <v>586</v>
+      </c>
+      <c r="I21" t="s">
+        <v>421</v>
+      </c>
+      <c r="J21" t="s">
+        <v>277</v>
+      </c>
+      <c r="N21" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;Omluva za zpoždění, špatná průjezdnost trasy.&lt;/displayName&gt;</v>
+      </c>
+      <c r="O21" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P21" s="23" t="str">
+        <f t="shared" si="14"/>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q21" s="23" t="str">
+        <f t="shared" si="15"/>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R21" s="23" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme se za zpoždění&amp;lt;br&amp;gt;způsobené špatnou průjezdností trasy.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We apologize for the delay caused by traffic.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S21" s="23" t="str">
+        <f t="shared" si="17"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T21" s="23" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U21" s="23" t="str">
+        <f t="shared" si="19"/>
+        <v>&lt;mp3&gt;H242.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V21" s="23" t="str">
+        <f t="shared" si="20"/>
+        <v>&lt;mp3&gt;H280.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="W21" s="23" t="str">
+        <f t="shared" si="21"/>
+        <v>&lt;mp3&gt;H160.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="X21" s="23" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="Y21" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Omluva za zpoždění, špatná průjezdnost trasy.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme se za zpoždění&amp;lt;br&amp;gt;způsobené špatnou průjezdností trasy.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We apologize for the delay caused by traffic.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H280.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="118.8" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B22" s="20">
+        <v>10</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24" t="s">
+        <v>582</v>
+      </c>
+      <c r="F22">
+        <v>6.8</v>
+      </c>
+      <c r="G22" s="3">
+        <v>7</v>
+      </c>
+      <c r="N22" s="23" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A22,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;změna pásma DEMO&lt;/displayName&gt;</v>
+      </c>
+      <c r="O22" s="23" t="str">
+        <f>CONCATENATE("&lt;",B$1,"&gt;",B22,"&lt;/",B$1,"&gt;")</f>
+        <v>&lt;duration&gt;10&lt;/duration&gt;</v>
+      </c>
+      <c r="P22" s="23" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C22,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;FareZoneChange&lt;/type&gt;</v>
+      </c>
+      <c r="Q22" s="23" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D22,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R22" s="23" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E22,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S22" s="23" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F22,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;6,8&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T22" s="23" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G22,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;7&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U22" s="23" t="str">
+        <f>IF(H22&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H22,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="V22" s="23" t="str">
+        <f>IF(I22&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I22,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W22" s="23" t="str">
+        <f>IF(J22&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J22,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X22" s="23" t="str">
+        <f>IF(K22&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K22,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y22" s="23" t="str">
+        <f>CONCATENATE("&lt;announcement&gt;",N22,O22,P22,Q22,R22,S22,T22,U22,V22,W22,X22,"&lt;/announcement&gt;")</f>
+        <v>&lt;announcement&gt;&lt;displayName&gt;změna pásma DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;FareZoneChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;6,8&lt;/changeFrom&gt;&lt;changeTo&gt;7&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" ht="118.8" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B23" s="20">
+        <v>10</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24" t="s">
+        <v>581</v>
+      </c>
+      <c r="F23">
+        <v>123</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="N23" s="23" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A23,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;změna linky DEMO&lt;/displayName&gt;</v>
+      </c>
+      <c r="O23" s="23" t="str">
+        <f>CONCATENATE("&lt;",B$1,"&gt;",B23,"&lt;/",B$1,"&gt;")</f>
+        <v>&lt;duration&gt;10&lt;/duration&gt;</v>
+      </c>
+      <c r="P23" s="23" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C23,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;LineChange&lt;/type&gt;</v>
+      </c>
+      <c r="Q23" s="23" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D23,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R23" s="23" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E23,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S23" s="23" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F23,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;123&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T23" s="23" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G23,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;XS2&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U23" s="23" t="str">
+        <f>IF(H23&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H23,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="V23" s="23" t="str">
+        <f>IF(I23&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I23,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W23" s="23" t="str">
+        <f>IF(J23&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J23,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X23" s="23" t="str">
+        <f>IF(K23&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K23,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y23" s="23" t="str">
+        <f>CONCATENATE("&lt;announcement&gt;",N23,O23,P23,Q23,R23,S23,T23,U23,V23,W23,X23,"&lt;/announcement&gt;")</f>
+        <v>&lt;announcement&gt;&lt;displayName&gt;změna linky DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;LineChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;123&lt;/changeFrom&gt;&lt;changeTo&gt;XS2&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A24" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="B24" s="20">
+        <v>5</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>576</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>575</v>
+      </c>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="N24" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;Letiště DEMO&lt;/displayName&gt;</v>
+      </c>
+      <c r="O24" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P24" s="23" t="str">
+        <f t="shared" si="14"/>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q24" s="23" t="str">
+        <f t="shared" si="15"/>
         <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Air&amp;quot;&amp;gt;\&amp;lt;/icon&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Odlety&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Flight
 departures&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/icon&gt;</v>
       </c>
-      <c r="R11" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E11,"&lt;/",E$1,"&gt;")</f>
+      <c r="R24" s="23" t="str">
+        <f t="shared" si="16"/>
         <v>&lt;text&gt;&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 1&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;lety do zemí mimo Schengenský prostor &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ flights to countries outside the Schengen Area&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 2&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
@@ -5065,32 +6125,32 @@
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 3&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;pouze soukromé lety &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ private flights only&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;&lt;/text&gt;</v>
       </c>
-      <c r="S11" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F11,"&lt;/",F$1,"&gt;")</f>
+      <c r="S24" s="23" t="str">
+        <f t="shared" si="17"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T11" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G11,"&lt;/",G$1,"&gt;")</f>
+      <c r="T24" s="23" t="str">
+        <f t="shared" si="18"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U11" t="str">
-        <f>IF(H11&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H11,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+      <c r="U24" s="23" t="str">
+        <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="V11" t="str">
-        <f>IF(I11&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I11,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="V24" s="23" t="str">
+        <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="W11" t="str">
-        <f>IF(J11&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J11,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="W24" s="23" t="str">
+        <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="X11" t="str">
-        <f>IF(K11&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K11,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+      <c r="X24" s="23" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Y11" t="str">
-        <f t="shared" si="8"/>
+      <c r="Y24" s="23" t="str">
+        <f t="shared" si="23"/>
         <v>&lt;announcement&gt;&lt;displayName&gt;Letiště DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Air&amp;quot;&amp;gt;\&amp;lt;/icon&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Odlety&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Flight
@@ -5102,381 +6162,163 @@
 &amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;pouze soukromé lety &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ private flights only&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="293.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
-        <v>604</v>
-      </c>
-      <c r="B12" s="24">
+    <row r="25" spans="1:25" ht="132" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B25" s="20">
         <v>5</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>569</v>
-      </c>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" t="s">
-        <v>421</v>
-      </c>
-      <c r="N12" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A12,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Zpoždění&lt;/displayName&gt;</v>
-      </c>
-      <c r="O12" t="str">
-        <f t="shared" si="1"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="24" t="s">
+        <v>567</v>
+      </c>
+      <c r="N25" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;zkrácený spoj DEMO&lt;/displayName&gt;</v>
+      </c>
+      <c r="O25" s="23" t="str">
+        <f t="shared" si="13"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P12" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C12,"&lt;/",C$1,"&gt;")</f>
+      <c r="P25" s="23" t="str">
+        <f t="shared" si="14"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q12" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D12,"&lt;/",D$1,"&gt;")</f>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Congestion&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R12" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E12,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme
-          se za zpoždění linky,
-          které je zapříčiněno silnou individiální
-          dopravou a špatnou průjezdností trasy&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-          &amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are sorry for delay
-          caused by heavy traffic and
-          limited passability of roads.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="S12" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F12,"&lt;/",F$1,"&gt;")</f>
-        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="T12" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G12,"&lt;/",G$1,"&gt;")</f>
-        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
-      </c>
-      <c r="U12" t="str">
-        <f>IF(H12&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H12,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v>&lt;mp3&gt;H280.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V12" t="str">
-        <f>IF(I12&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I12,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W12" t="str">
-        <f>IF(J12&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J12,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="X12" t="str">
-        <f>IF(K12&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K12,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y12" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Zpoždění&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Congestion&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme
-          se za zpoždění linky,
-          které je zapříčiněno silnou individiální
-          dopravou a špatnou průjezdností trasy&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-          &amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are sorry for delay
-          caused by heavy traffic and
-          limited passability of roads.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H280.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="102" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="B13" s="24">
-        <v>10</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>611</v>
-      </c>
-      <c r="F13">
-        <v>6.8</v>
-      </c>
-      <c r="G13" s="3">
-        <v>7</v>
-      </c>
-      <c r="N13" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A13,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;změna pásma DEMO&lt;/displayName&gt;</v>
-      </c>
-      <c r="O13" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;duration&gt;10&lt;/duration&gt;</v>
-      </c>
-      <c r="P13" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C13,"&lt;/",C$1,"&gt;")</f>
-        <v>&lt;type&gt;FareZoneChange&lt;/type&gt;</v>
-      </c>
-      <c r="Q13" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D13,"&lt;/",D$1,"&gt;")</f>
+      <c r="Q25" s="23" t="str">
+        <f t="shared" si="15"/>
         <v>&lt;icon&gt;&lt;/icon&gt;</v>
       </c>
-      <c r="R13" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E13,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="S13" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F13,"&lt;/",F$1,"&gt;")</f>
-        <v>&lt;changeFrom&gt;6,8&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="T13" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G13,"&lt;/",G$1,"&gt;")</f>
-        <v>&lt;changeTo&gt;7&lt;/changeTo&gt;</v>
-      </c>
-      <c r="U13" t="str">
-        <f>IF(H13&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H13,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V13" t="str">
-        <f>IF(I13&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I13,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W13" t="str">
-        <f>IF(J13&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J13,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="X13" t="str">
-        <f>IF(K13&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K13,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y13" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;změna pásma DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;FareZoneChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;6,8&lt;/changeFrom&gt;&lt;changeTo&gt;7&lt;/changeTo&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="B14" s="24">
-        <v>10</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>610</v>
-      </c>
-      <c r="F14">
-        <v>123</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="N14" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A14,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;změna linky DEMO&lt;/displayName&gt;</v>
-      </c>
-      <c r="O14" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;duration&gt;10&lt;/duration&gt;</v>
-      </c>
-      <c r="P14" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C14,"&lt;/",C$1,"&gt;")</f>
-        <v>&lt;type&gt;LineChange&lt;/type&gt;</v>
-      </c>
-      <c r="Q14" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D14,"&lt;/",D$1,"&gt;")</f>
-        <v>&lt;icon&gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R14" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E14,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="S14" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F14,"&lt;/",F$1,"&gt;")</f>
-        <v>&lt;changeFrom&gt;123&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="T14" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G14,"&lt;/",G$1,"&gt;")</f>
-        <v>&lt;changeTo&gt;XS2&lt;/changeTo&gt;</v>
-      </c>
-      <c r="U14" t="str">
-        <f>IF(H14&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H14,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V14" t="str">
-        <f>IF(I14&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I14,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W14" t="str">
-        <f>IF(J14&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J14,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="X14" t="str">
-        <f>IF(K14&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K14,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y14" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;změna linky DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;LineChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;123&lt;/changeFrom&gt;&lt;changeTo&gt;XS2&lt;/changeTo&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="B15" s="24">
-        <v>5</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>581</v>
-      </c>
-      <c r="N15" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A15,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;zkrácený spoj DEMO&lt;/displayName&gt;</v>
-      </c>
-      <c r="O15" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
-      </c>
-      <c r="P15" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C15,"&lt;/",C$1,"&gt;")</f>
-        <v>&lt;type&gt;&lt;/type&gt;</v>
-      </c>
-      <c r="Q15" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D15,"&lt;/",D$1,"&gt;")</f>
-        <v>&lt;icon&gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R15" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E15,"&lt;/",E$1,"&gt;")</f>
+      <c r="R25" s="23" t="str">
+        <f t="shared" si="16"/>
         <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;Upozorňujeme cestující, že tento spoj končí v zastávce &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please, this bus terminates at &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;  &lt;/text&gt;</v>
       </c>
-      <c r="S15" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F15,"&lt;/",F$1,"&gt;")</f>
+      <c r="S25" s="23" t="str">
+        <f t="shared" si="17"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T15" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G15,"&lt;/",G$1,"&gt;")</f>
+      <c r="T25" s="23" t="str">
+        <f t="shared" si="18"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U15" t="str">
-        <f>IF(H15&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H15,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+      <c r="U25" s="23" t="str">
+        <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="V15" t="str">
-        <f>IF(I15&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I15,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="V25" s="23" t="str">
+        <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="W15" t="str">
-        <f>IF(J15&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J15,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="W25" s="23" t="str">
+        <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="X15" t="str">
-        <f>IF(K15&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K15,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+      <c r="X25" s="23" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Y15" t="str">
-        <f t="shared" si="8"/>
+      <c r="Y25" s="23" t="str">
+        <f t="shared" si="23"/>
         <v>&lt;announcement&gt;&lt;displayName&gt;zkrácený spoj DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;Upozorňujeme cestující, že tento spoj končí v zastávce &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please, this bus terminates at &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;  &lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="B16" s="24">
-        <v>5</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>559</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>583</v>
-      </c>
-      <c r="N16" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A16,"&lt;/",A$1,"&gt;")</f>
+    <row r="26" spans="1:25" ht="158.4" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="B26" s="20">
+        <v>10</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>625</v>
+      </c>
+      <c r="N26" s="23" t="str">
+        <f t="shared" si="12"/>
         <v>&lt;displayName&gt;info o výluce DEMO&lt;/displayName&gt;</v>
       </c>
-      <c r="O16" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
-      </c>
-      <c r="P16" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C16,"&lt;/",C$1,"&gt;")</f>
+      <c r="O26" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>&lt;duration&gt;10&lt;/duration&gt;</v>
+      </c>
+      <c r="P26" s="23" t="str">
+        <f t="shared" si="14"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q16" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D16,"&lt;/",D$1,"&gt;")</f>
+      <c r="Q26" s="23" t="str">
+        <f t="shared" si="15"/>
         <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
       </c>
-      <c r="R16" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E16,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;&amp;lt;font type=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Koh-i-noor – Bělocerkevská&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font type=&amp;quot;48&amp;quot;&amp;gt;Vážení cestující, z důvodu opravy komunikace je linka v tomto úseku odkloněna po náhradní trase. Zastávky Kavkazská, Na Míčánkách a Bělocerkevská jsou vynechány.&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="S16" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F16,"&lt;/",F$1,"&gt;")</f>
+      <c r="R26" s="23" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Koh-i-noor – Bělocerkevská&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;Vážení cestující, z důvodu opravy komunikace je linka v tomto úseku odkloněna po náhradní trase. Zastávky Kavkazská, Na Míčánkách a Bělocerkevská jsou vynechány.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S26" s="23" t="str">
+        <f t="shared" si="17"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T16" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G16,"&lt;/",G$1,"&gt;")</f>
+      <c r="T26" s="23" t="str">
+        <f t="shared" si="18"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U16" t="str">
-        <f>IF(H16&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H16,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+      <c r="U26" s="23" t="str">
+        <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="V16" t="str">
-        <f>IF(I16&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I16,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="V26" s="23" t="str">
+        <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="W16" t="str">
-        <f>IF(J16&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J16,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="W26" s="23" t="str">
+        <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="X16" t="str">
-        <f>IF(K16&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K16,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+      <c r="X26" s="23" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Y16" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;info o výluce DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font type=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Koh-i-noor – Bělocerkevská&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font type=&amp;quot;48&amp;quot;&amp;gt;Vážení cestující, z důvodu opravy komunikace je linka v tomto úseku odkloněna po náhradní trase. Zastávky Kavkazská, Na Míčánkách a Bělocerkevská jsou vynechány.&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" ht="255" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="B17" s="24">
-        <v>5</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>566</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>585</v>
-      </c>
-      <c r="N17" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A17,"&lt;/",A$1,"&gt;")</f>
+      <c r="Y26" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;info o výluce DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Koh-i-noor – Bělocerkevská&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;Vážení cestující, z důvodu opravy komunikace je linka v tomto úseku odkloněna po náhradní trase. Zastávky Kavkazská, Na Míčánkách a Bělocerkevská jsou vynechány.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="303.60000000000002" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B27" s="20">
+        <v>15</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>570</v>
+      </c>
+      <c r="N27" s="23" t="str">
+        <f t="shared" si="12"/>
         <v>&lt;displayName&gt;trvalá změna DEMO&lt;/displayName&gt;</v>
       </c>
-      <c r="O17" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
-      </c>
-      <c r="P17" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C17,"&lt;/",C$1,"&gt;")</f>
+      <c r="O27" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>&lt;duration&gt;15&lt;/duration&gt;</v>
+      </c>
+      <c r="P27" s="23" t="str">
+        <f t="shared" si="14"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q17" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D17,"&lt;/",D$1,"&gt;")</f>
+      <c r="Q27" s="23" t="str">
+        <f t="shared" si="15"/>
         <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
       </c>
-      <c r="R17" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E17,"&lt;/",E$1,"&gt;")</f>
+      <c r="R27" s="23" t="str">
+        <f t="shared" si="16"/>
         <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Změna linkového vedení BUS&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. září 2018&amp;lt;/b&amp;gt; dochází k trvalé změně linkového vedení
 autobusů PID &amp;lt;b&amp;gt;v oblasti Radotínska&amp;lt;/b&amp;gt;. Podrobnosti naleznete
@@ -5486,33 +6328,33 @@
 will take place in operation of the PID system &amp;lt;b&amp;gt;in Radotín area&amp;lt;/b&amp;gt;. Visit &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt; for more
 information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
       </c>
-      <c r="S17" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F17,"&lt;/",F$1,"&gt;")</f>
+      <c r="S27" s="23" t="str">
+        <f t="shared" si="17"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T17" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G17,"&lt;/",G$1,"&gt;")</f>
+      <c r="T27" s="23" t="str">
+        <f t="shared" si="18"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U17" t="str">
-        <f>IF(H17&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H17,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+      <c r="U27" s="23" t="str">
+        <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="V17" t="str">
-        <f>IF(I17&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I17,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="V27" s="23" t="str">
+        <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="W17" t="str">
-        <f>IF(J17&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J17,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="W27" s="23" t="str">
+        <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="X17" t="str">
-        <f>IF(K17&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K17,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+      <c r="X27" s="23" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Y17" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;trvalá změna DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Změna linkového vedení BUS&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+      <c r="Y27" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;trvalá změna DEMO&lt;/displayName&gt;&lt;duration&gt;15&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Změna linkového vedení BUS&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. září 2018&amp;lt;/b&amp;gt; dochází k trvalé změně linkového vedení
 autobusů PID &amp;lt;b&amp;gt;v oblasti Radotínska&amp;lt;/b&amp;gt;. Podrobnosti naleznete
 na zastávkách a na &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
@@ -5522,37 +6364,37 @@
 information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="344.25" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="B18" s="24">
-        <v>5</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>588</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>587</v>
-      </c>
-      <c r="N18" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A18,"&lt;/",A$1,"&gt;")</f>
+    <row r="28" spans="1:25" ht="396" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="B28" s="20">
+        <v>15</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>572</v>
+      </c>
+      <c r="N28" s="23" t="str">
+        <f t="shared" si="12"/>
         <v>&lt;displayName&gt;Jiné sdělení DEMO&lt;/displayName&gt;</v>
       </c>
-      <c r="O18" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
-      </c>
-      <c r="P18" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C18,"&lt;/",C$1,"&gt;")</f>
+      <c r="O28" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>&lt;duration&gt;15&lt;/duration&gt;</v>
+      </c>
+      <c r="P28" s="23" t="str">
+        <f t="shared" si="14"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q18" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D18,"&lt;/",D$1,"&gt;")</f>
+      <c r="Q28" s="23" t="str">
+        <f t="shared" si="15"/>
         <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
       </c>
-      <c r="R18" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E18,"&lt;/",E$1,"&gt;")</f>
+      <c r="R28" s="23" t="str">
+        <f t="shared" si="16"/>
         <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Zastávky na znamení od 1. 7. 2019&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. července 2019&amp;lt;/b&amp;gt; budou všechny autobusové zastávky
 na území hl. m. Prahy na znamení. Na autobus není nutné mávat,
@@ -5563,33 +6405,33 @@
 You don‘t have lift a hand to stop the bus, &amp;lt;b&amp;gt;just stand in the bus stop area&amp;lt;/b&amp;gt;. Press the
 &amp;lt;b&amp;gt;STOP button or the door button&amp;lt;/b&amp;gt;. Visit &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt; for more information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
       </c>
-      <c r="S18" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F18,"&lt;/",F$1,"&gt;")</f>
+      <c r="S28" s="23" t="str">
+        <f t="shared" si="17"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T18" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G18,"&lt;/",G$1,"&gt;")</f>
+      <c r="T28" s="23" t="str">
+        <f t="shared" si="18"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U18" t="str">
-        <f>IF(H18&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H18,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+      <c r="U28" s="23" t="str">
+        <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="V18" t="str">
-        <f>IF(I18&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I18,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="V28" s="23" t="str">
+        <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="W18" t="str">
-        <f>IF(J18&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J18,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="W28" s="23" t="str">
+        <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="X18" t="str">
-        <f>IF(K18&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K18,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+      <c r="X28" s="23" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Y18" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Jiné sdělení DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Zastávky na znamení od 1. 7. 2019&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+      <c r="Y28" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Jiné sdělení DEMO&lt;/displayName&gt;&lt;duration&gt;15&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Zastávky na znamení od 1. 7. 2019&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. července 2019&amp;lt;/b&amp;gt; budou všechny autobusové zastávky
 na území hl. m. Prahy na znamení. Na autobus není nutné mávat,
 &amp;lt;b&amp;gt;stačí stát viditelně na zastávce&amp;lt;/b&amp;gt;. Před výstupem stiskněte
@@ -5600,606 +6442,384 @@
 &amp;lt;b&amp;gt;STOP button or the door button&amp;lt;/b&amp;gt;. Visit &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt; for more information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="216.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="B19" s="24">
+    <row r="29" spans="1:25" ht="198" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="B29" s="20">
         <v>15</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>607</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>606</v>
-      </c>
-      <c r="N19" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A19,"&lt;/",A$1,"&gt;")</f>
+      <c r="D29" s="24" t="s">
+        <v>578</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>629</v>
+      </c>
+      <c r="N29" s="23" t="str">
+        <f t="shared" si="12"/>
         <v>&lt;displayName&gt;Zpráva z dispečinku DEMO&lt;/displayName&gt;</v>
       </c>
-      <c r="O19" t="str">
-        <f t="shared" si="1"/>
+      <c r="O29" s="23" t="str">
+        <f t="shared" si="13"/>
         <v>&lt;duration&gt;15&lt;/duration&gt;</v>
       </c>
-      <c r="P19" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C19,"&lt;/",C$1,"&gt;")</f>
+      <c r="P29" s="23" t="str">
+        <f t="shared" si="14"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q19" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D19,"&lt;/",D$1,"&gt;")</f>
+      <c r="Q29" s="23" t="str">
+        <f t="shared" si="15"/>
         <v>&lt;icon&gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
     &amp;lt;icon type=&amp;quot;c_Exclamation&amp;quot;&amp;gt;!&amp;lt;/icon&amp;gt;
 &amp;lt;/color&amp;gt;    &lt;/icon&gt;</v>
       </c>
-      <c r="R19" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E19,"&lt;/",E$1,"&gt;")</f>
+      <c r="R29" s="23" t="str">
+        <f t="shared" si="16"/>
         <v>&lt;text&gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
 &amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;            
-    Z důvodu sněhové kalamity je ulice Horoměřická neprůjezdná.
-    Linky 316 a 356 jsou ze zastávky Statenice, Černý Vůl, hospoda
-    vedeny odklonem přes zastávky Výhledy, Zemědělská univerzita,
-    V Podbabě a Nádraží Podbaba do zastávky Dejvická (přestup
-    na metro „A“).&amp;lt;br&amp;gt;
-    Pravidelný povoz bude obnoven po zajištění sjízdnosti všech
-    komunikací (během dnešního odpoledne).
+Z důvodu sněhové kalamity je ulice Horoměřická neprůjezdná. Linky 316 a 356 jsou ze zastávky Statenice, Černý Vůl, hospoda vedeny odklonem přes zastávky Výhledy, Zemědělská univerzita, V Podbabě a Nádraží Podbaba do zastávky Dejvická (přestup na metro „A“).&amp;lt;br&amp;gt;Pravidelný povoz bude obnoven po zajištění sjízdnosti všech komunikací (během dnešního odpoledne).
 &amp;lt;/font&amp;gt;
 &amp;lt;/color&amp;gt;&lt;/text&gt;</v>
       </c>
-      <c r="S19" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F19,"&lt;/",F$1,"&gt;")</f>
+      <c r="S29" s="23" t="str">
+        <f t="shared" si="17"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T19" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G19,"&lt;/",G$1,"&gt;")</f>
+      <c r="T29" s="23" t="str">
+        <f t="shared" si="18"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U19" t="str">
-        <f>IF(H19&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H19,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+      <c r="U29" s="23" t="str">
+        <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="V19" t="str">
-        <f>IF(I19&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I19,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="V29" s="23" t="str">
+        <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="W19" t="str">
-        <f>IF(J19&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J19,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="W29" s="23" t="str">
+        <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="X19" t="str">
-        <f>IF(K19&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K19,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+      <c r="X29" s="23" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Y19" t="str">
-        <f t="shared" si="8"/>
+      <c r="Y29" s="23" t="str">
+        <f t="shared" si="23"/>
         <v>&lt;announcement&gt;&lt;displayName&gt;Zpráva z dispečinku DEMO&lt;/displayName&gt;&lt;duration&gt;15&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
     &amp;lt;icon type=&amp;quot;c_Exclamation&amp;quot;&amp;gt;!&amp;lt;/icon&amp;gt;
 &amp;lt;/color&amp;gt;    &lt;/icon&gt;&lt;text&gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
 &amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;            
-    Z důvodu sněhové kalamity je ulice Horoměřická neprůjezdná.
-    Linky 316 a 356 jsou ze zastávky Statenice, Černý Vůl, hospoda
-    vedeny odklonem přes zastávky Výhledy, Zemědělská univerzita,
-    V Podbabě a Nádraží Podbaba do zastávky Dejvická (přestup
-    na metro „A“).&amp;lt;br&amp;gt;
-    Pravidelný povoz bude obnoven po zajištění sjízdnosti všech
-    komunikací (během dnešního odpoledne).
+Z důvodu sněhové kalamity je ulice Horoměřická neprůjezdná. Linky 316 a 356 jsou ze zastávky Statenice, Černý Vůl, hospoda vedeny odklonem přes zastávky Výhledy, Zemědělská univerzita, V Podbabě a Nádraží Podbaba do zastávky Dejvická (přestup na metro „A“).&amp;lt;br&amp;gt;Pravidelný povoz bude obnoven po zajištění sjízdnosti všech komunikací (během dnešního odpoledne).
 &amp;lt;/font&amp;gt;
 &amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="30" spans="1:25" ht="19.2" x14ac:dyDescent="0.45">
+      <c r="A30" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B30" s="20">
         <v>5</v>
       </c>
-      <c r="D20" s="23" t="s">
-        <v>588</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>454</v>
-      </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" t="s">
-        <v>453</v>
-      </c>
-      <c r="N20" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A20,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Funkčnost klimatizace&lt;/displayName&gt;</v>
-      </c>
-      <c r="O20" t="str">
-        <f t="shared" si="1"/>
+      <c r="D30" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" t="s">
+        <v>348</v>
+      </c>
+      <c r="N30" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;Nastupujte předními dveřmi&lt;/displayName&gt;</v>
+      </c>
+      <c r="O30" s="23" t="str">
+        <f t="shared" si="13"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P20" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C20,"&lt;/",C$1,"&gt;")</f>
+      <c r="P30" s="23" t="str">
+        <f t="shared" si="14"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q20" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D20,"&lt;/",D$1,"&gt;")</f>
+      <c r="Q30" s="23" t="str">
+        <f t="shared" si="15"/>
         <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
       </c>
-      <c r="R20" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E20,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;Vážení cestující, pro správnou funkčnost klimatizace v tomto vozidle, která je nyní v provozu, prosíme neotevírejte boční okna ani stropní poklopy. Děkujeme Vám za pochopení.&lt;/text&gt;</v>
-      </c>
-      <c r="S20" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F20,"&lt;/",F$1,"&gt;")</f>
+      <c r="R30" s="23" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;text&gt;Prosíme, nastupujte předními dveřmi.&lt;/text&gt;</v>
+      </c>
+      <c r="S30" s="23" t="str">
+        <f t="shared" si="17"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T20" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G20,"&lt;/",G$1,"&gt;")</f>
+      <c r="T30" s="23" t="str">
+        <f t="shared" si="18"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U20" t="str">
-        <f>IF(H20&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H20,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v>&lt;mp3&gt;H350.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V20" t="str">
-        <f>IF(I20&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I20,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="U30" s="23" t="str">
+        <f t="shared" si="19"/>
+        <v>&lt;mp3&gt;H205.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V30" s="23" t="str">
+        <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="W20" t="str">
-        <f>IF(J20&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J20,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="W30" s="23" t="str">
+        <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="X20" t="str">
-        <f>IF(K20&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K20,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+      <c r="X30" s="23" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Y20" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Funkčnost klimatizace&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Vážení cestující, pro správnou funkčnost klimatizace v tomto vozidle, která je nyní v provozu, prosíme neotevírejte boční okna ani stropní poklopy. Děkujeme Vám za pochopení.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H350.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="Y30" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Nastupujte předními dveřmi&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Prosíme, nastupujte předními dveřmi.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H205.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="19.2" x14ac:dyDescent="0.45">
+      <c r="A31" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B31" s="20">
         <v>5</v>
       </c>
-      <c r="D21" s="23" t="s">
-        <v>588</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" t="s">
-        <v>348</v>
-      </c>
-      <c r="N21" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A21,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Nastupujte předními dveřmi&lt;/displayName&gt;</v>
-      </c>
-      <c r="O21" t="str">
-        <f t="shared" si="1"/>
+      <c r="D31" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" t="s">
+        <v>317</v>
+      </c>
+      <c r="N31" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;Přední dveře, předložte doklad&lt;/displayName&gt;</v>
+      </c>
+      <c r="O31" s="23" t="str">
+        <f t="shared" si="13"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P21" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C21,"&lt;/",C$1,"&gt;")</f>
+      <c r="P31" s="23" t="str">
+        <f t="shared" si="14"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q21" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D21,"&lt;/",D$1,"&gt;")</f>
+      <c r="Q31" s="23" t="str">
+        <f t="shared" si="15"/>
         <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
       </c>
-      <c r="R21" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E21,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;Prosíme, nastupujte předními dveřmi.&lt;/text&gt;</v>
-      </c>
-      <c r="S21" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F21,"&lt;/",F$1,"&gt;")</f>
+      <c r="R31" s="23" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;text&gt;Nástup předními dveřmi. Předložte prosím jízdní doklad.&lt;/text&gt;</v>
+      </c>
+      <c r="S31" s="23" t="str">
+        <f t="shared" si="17"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T21" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G21,"&lt;/",G$1,"&gt;")</f>
+      <c r="T31" s="23" t="str">
+        <f t="shared" si="18"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U21" t="str">
-        <f>IF(H21&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H21,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v>&lt;mp3&gt;H205.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V21" t="str">
-        <f>IF(I21&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I21,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="U31" s="23" t="str">
+        <f t="shared" si="19"/>
+        <v>&lt;mp3&gt;H183.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V31" s="23" t="str">
+        <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="W21" t="str">
-        <f>IF(J21&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J21,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="W31" s="23" t="str">
+        <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="X21" t="str">
-        <f>IF(K21&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K21,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+      <c r="X31" s="23" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Y21" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Nastupujte předními dveřmi&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Prosíme, nastupujte předními dveřmi.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H205.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="Y31" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Přední dveře, předložte doklad&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Nástup předními dveřmi. Předložte prosím jízdní doklad.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H183.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="19.2" x14ac:dyDescent="0.45">
+      <c r="A32" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B32" s="20">
         <v>5</v>
       </c>
-      <c r="D22" s="23" t="s">
-        <v>588</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" t="s">
-        <v>281</v>
-      </c>
-      <c r="N22" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A22,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Neprůjezdnost, linka ukončena&lt;/displayName&gt;</v>
-      </c>
-      <c r="O22" t="str">
-        <f t="shared" si="1"/>
+      <c r="D32" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" t="s">
+        <v>315</v>
+      </c>
+      <c r="N32" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;Uvolněte přední dveře&lt;/displayName&gt;</v>
+      </c>
+      <c r="O32" s="23" t="str">
+        <f t="shared" si="13"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P22" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C22,"&lt;/",C$1,"&gt;")</f>
+      <c r="P32" s="23" t="str">
+        <f t="shared" si="14"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q22" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D22,"&lt;/",D$1,"&gt;")</f>
+      <c r="Q32" s="23" t="str">
+        <f t="shared" si="15"/>
         <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
       </c>
-      <c r="R22" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E22,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;Linka je z důvodu neprůjezdnosti trasy dočasně zkrácena.&lt;/text&gt;</v>
-      </c>
-      <c r="S22" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F22,"&lt;/",F$1,"&gt;")</f>
+      <c r="R32" s="23" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;text&gt;Uvolněte prosím prostor předních dveří.&lt;/text&gt;</v>
+      </c>
+      <c r="S32" s="23" t="str">
+        <f t="shared" si="17"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T22" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G22,"&lt;/",G$1,"&gt;")</f>
+      <c r="T32" s="23" t="str">
+        <f t="shared" si="18"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U22" t="str">
-        <f>IF(H22&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H22,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v>&lt;mp3&gt;H162.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V22" t="str">
-        <f>IF(I22&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I22,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="U32" s="23" t="str">
+        <f t="shared" si="19"/>
+        <v>&lt;mp3&gt;H182.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V32" s="23" t="str">
+        <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="W22" t="str">
-        <f>IF(J22&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J22,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="W32" s="23" t="str">
+        <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="X22" t="str">
-        <f>IF(K22&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K22,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+      <c r="X32" s="23" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Y22" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Neprůjezdnost, linka ukončena&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Linka je z důvodu neprůjezdnosti trasy dočasně zkrácena.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H162.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="60" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="Y32" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Uvolněte přední dveře&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Uvolněte prosím prostor předních dveří.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H182.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" ht="19.2" x14ac:dyDescent="0.45">
+      <c r="A33" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B33" s="20">
         <v>5</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>559</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" t="s">
-        <v>285</v>
-      </c>
-      <c r="N23" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A23,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Neprůjezdnost, odklon&lt;/displayName&gt;</v>
-      </c>
-      <c r="O23" t="str">
-        <f t="shared" si="1"/>
+      <c r="D33" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" t="s">
+        <v>340</v>
+      </c>
+      <c r="N33" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>&lt;displayName&gt;Vozidlo obsazeno&lt;/displayName&gt;</v>
+      </c>
+      <c r="O33" s="23" t="str">
+        <f t="shared" si="13"/>
         <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
-      <c r="P23" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C23,"&lt;/",C$1,"&gt;")</f>
+      <c r="P33" s="23" t="str">
+        <f t="shared" si="14"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="Q23" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D23,"&lt;/",D$1,"&gt;")</f>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R23" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E23,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;Z důvodu neprůjezdnosti je linka vedena po odklonové trase.&lt;/text&gt;</v>
-      </c>
-      <c r="S23" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F23,"&lt;/",F$1,"&gt;")</f>
+      <c r="Q33" s="23" t="str">
+        <f t="shared" si="15"/>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R33" s="23" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;text&gt;Vozidlo plně obsazeno. Vyčkejte prosím na další spoj.&lt;/text&gt;</v>
+      </c>
+      <c r="S33" s="23" t="str">
+        <f t="shared" si="17"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="T23" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G23,"&lt;/",G$1,"&gt;")</f>
+      <c r="T33" s="23" t="str">
+        <f t="shared" si="18"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="U23" t="str">
-        <f>IF(H23&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H23,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v>&lt;mp3&gt;H164.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V23" t="str">
-        <f>IF(I23&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I23,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+      <c r="U33" s="23" t="str">
+        <f t="shared" si="19"/>
+        <v>&lt;mp3&gt;H201.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V33" s="23" t="str">
+        <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="W23" t="str">
-        <f>IF(J23&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J23,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+      <c r="W33" s="23" t="str">
+        <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="X23" t="str">
-        <f>IF(K23&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K23,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+      <c r="X33" s="23" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Y23" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Neprůjezdnost, odklon&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Z důvodu neprůjezdnosti je linka vedena po odklonové trase.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H164.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>527</v>
-      </c>
-      <c r="B24" s="24">
-        <v>5</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>588</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="N24" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A24,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Přední dveře, předložte doklad&lt;/displayName&gt;</v>
-      </c>
-      <c r="O24" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
-      </c>
-      <c r="P24" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C24,"&lt;/",C$1,"&gt;")</f>
-        <v>&lt;type&gt;&lt;/type&gt;</v>
-      </c>
-      <c r="Q24" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D24,"&lt;/",D$1,"&gt;")</f>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R24" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E24,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;Nástup předními dveřmi. Předložte prosím jízdní doklad.&lt;/text&gt;</v>
-      </c>
-      <c r="S24" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F24,"&lt;/",F$1,"&gt;")</f>
-        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="T24" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G24,"&lt;/",G$1,"&gt;")</f>
-        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
-      </c>
-      <c r="U24" t="str">
-        <f>IF(H24&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H24,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v>&lt;mp3&gt;H183.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V24" t="str">
-        <f>IF(I24&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I24,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W24" t="str">
-        <f>IF(J24&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J24,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="X24" t="str">
-        <f>IF(K24&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K24,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y24" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Přední dveře, předložte doklad&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Nástup předními dveřmi. Předložte prosím jízdní doklad.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H183.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>528</v>
-      </c>
-      <c r="B25" s="24">
-        <v>5</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>588</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" t="s">
-        <v>315</v>
-      </c>
-      <c r="N25" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A25,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Uvolněte přední dveře&lt;/displayName&gt;</v>
-      </c>
-      <c r="O25" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
-      </c>
-      <c r="P25" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C25,"&lt;/",C$1,"&gt;")</f>
-        <v>&lt;type&gt;&lt;/type&gt;</v>
-      </c>
-      <c r="Q25" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D25,"&lt;/",D$1,"&gt;")</f>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R25" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E25,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;Uvolněte prosím prostor předních dveří.&lt;/text&gt;</v>
-      </c>
-      <c r="S25" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F25,"&lt;/",F$1,"&gt;")</f>
-        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="T25" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G25,"&lt;/",G$1,"&gt;")</f>
-        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
-      </c>
-      <c r="U25" t="str">
-        <f>IF(H25&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H25,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v>&lt;mp3&gt;H182.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V25" t="str">
-        <f>IF(I25&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I25,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W25" t="str">
-        <f>IF(J25&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J25,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="X25" t="str">
-        <f>IF(K25&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K25,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y25" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Uvolněte přední dveře&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Uvolněte prosím prostor předních dveří.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H182.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>529</v>
-      </c>
-      <c r="B26" s="24">
-        <v>5</v>
-      </c>
-      <c r="D26" s="23" t="s">
-        <v>588</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" t="s">
-        <v>340</v>
-      </c>
-      <c r="N26" t="str">
-        <f>CONCATENATE("&lt;",A$1,"&gt;",A26,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Vozidlo obsazeno&lt;/displayName&gt;</v>
-      </c>
-      <c r="O26" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
-      </c>
-      <c r="P26" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C26,"&lt;/",C$1,"&gt;")</f>
-        <v>&lt;type&gt;&lt;/type&gt;</v>
-      </c>
-      <c r="Q26" t="str">
-        <f>CONCATENATE("&lt;",D$1,"&gt;",D26,"&lt;/",D$1,"&gt;")</f>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="R26" t="str">
-        <f>CONCATENATE("&lt;",E$1,"&gt;",E26,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;text&gt;Vozidlo plně obsazeno. Vyčkejte prosím na další spoj.&lt;/text&gt;</v>
-      </c>
-      <c r="S26" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F26,"&lt;/",F$1,"&gt;")</f>
-        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="T26" t="str">
-        <f>CONCATENATE("&lt;",G$1,"&gt;",G26,"&lt;/",G$1,"&gt;")</f>
-        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
-      </c>
-      <c r="U26" t="str">
-        <f>IF(H26&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H26,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v>&lt;mp3&gt;H201.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="V26" t="str">
-        <f>IF(I26&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I26,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W26" t="str">
-        <f>IF(J26&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J26,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="X26" t="str">
-        <f>IF(K26&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K26,".mp3","&lt;/",K$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="Y26" t="str">
-        <f t="shared" si="8"/>
+      <c r="Y33" s="23" t="str">
+        <f t="shared" si="23"/>
         <v>&lt;announcement&gt;&lt;displayName&gt;Vozidlo obsazeno&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Vozidlo plně obsazeno. Vyčkejte prosím na další spoj.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H201.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E20:G20">
-    <cfRule type="duplicateValues" dxfId="18" priority="15" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3:G3">
-    <cfRule type="duplicateValues" dxfId="17" priority="14" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21:G21">
-    <cfRule type="duplicateValues" dxfId="16" priority="13" stopIfTrue="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E2:G2">
     <cfRule type="duplicateValues" dxfId="15" priority="12" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E22:G22">
-    <cfRule type="duplicateValues" dxfId="14" priority="16" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E23:G23">
-    <cfRule type="duplicateValues" dxfId="13" priority="3" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E3:G3">
+    <cfRule type="duplicateValues" dxfId="14" priority="14" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:G4">
-    <cfRule type="duplicateValues" dxfId="12" priority="5" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="5" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E24:G24">
-    <cfRule type="duplicateValues" dxfId="11" priority="11" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E25:G25">
-    <cfRule type="duplicateValues" dxfId="10" priority="10" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E26:G26">
-    <cfRule type="duplicateValues" dxfId="9" priority="9" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7:G7">
-    <cfRule type="duplicateValues" dxfId="8" priority="8" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E5:G5">
+    <cfRule type="duplicateValues" dxfId="12" priority="123" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:G6">
-    <cfRule type="duplicateValues" dxfId="7" priority="1" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:G5">
-    <cfRule type="duplicateValues" dxfId="6" priority="123" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E12:G12">
-    <cfRule type="duplicateValues" dxfId="5" priority="124" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="15" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E8:G9 E11:G11 F10:G10">
-    <cfRule type="duplicateValues" dxfId="4" priority="125" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E21:G21">
+    <cfRule type="duplicateValues" dxfId="9" priority="128" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24:G24 E13:G19 F20:G20">
+    <cfRule type="duplicateValues" dxfId="8" priority="125" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30:G30">
+    <cfRule type="duplicateValues" dxfId="7" priority="13" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31:G31">
+    <cfRule type="duplicateValues" dxfId="6" priority="11" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E32:G32">
+    <cfRule type="duplicateValues" dxfId="5" priority="10" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E33:G33">
+    <cfRule type="duplicateValues" dxfId="4" priority="9" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -6209,32 +6829,41 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9852E3C-683B-43DE-923C-E58C5265AC8A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="str">
         <f>_xlfn.TEXTJOIN("",TRUE,"&lt;announcementList&gt;",slozit!Y:Y,"&lt;/announcementList&gt;")</f>
-        <v>&lt;announcementList&gt;&lt;announcement&gt;&lt;displayName&gt;Zavazadla&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Luggage&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že pokládat
-zavazadla na sedadla není dovoleno.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H239.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Zákaz jídla a pití &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že konzumace
-potravin není ve vozidlech povolena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not eat any food in the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H340.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Kočárek&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pram&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
-místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H240.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Invalidní vozík&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_WheelChair&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
-místo pro invalidní vozík.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a wheelchair.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H260.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Postupujte dále do vozu&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_GoFurther&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,
-          postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-          &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further
-          into the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H179.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vyčkávání na čas odjezdu&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu
-dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled
-departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H281.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vzájemný přestup&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Bus&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for a mutual transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H284.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vzájemný přestup (vlak)&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_SBahn&amp;quot;&amp;gt;~&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přestup z vlakové linky S dle stanovené čekací doby.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for an „S“ train transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Odklon&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
-&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu silné automobilové dopravy
-pojede tato linka odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;This line will be rerouted due to heavy traffic.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
-&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H279.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Letiště DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Air&amp;quot;&amp;gt;\&amp;lt;/icon&amp;gt;&amp;lt;br&amp;gt;
+        <v>&lt;announcementList&gt;&lt;announcement&gt;&lt;displayName&gt;Nepokládejte zavazadla na sedadla. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Luggage&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Nepokládejte zavazadla na sedadla.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H339.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Zákaz konzumace potravin ve voze. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Konzumace potravin ve voze není povolena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not eat in the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H340.mp3&lt;/mp3&gt;&lt;mp3&gt;H740.mp3&lt;/mp3&gt;&lt;mp3&gt;H741.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Uvolněte prostor pro kočárek. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pram&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,&amp;lt;br&amp;gt;místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please make room for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H240.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Uvolněte prostor pro invalidní vozík. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_WheelChair&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,&amp;lt;br&amp;gt;prostor pro invalidní vozík.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please make room for a wheelchair.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H260.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Uvolněte přední dveře, postupte dále do vozu. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,&amp;lt;br&amp;gt;postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further inside the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H206.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vyčkáváme na odjezd dle jízdního řádu. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H281.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Přepravní kontrola, připravte si cestovní doklady. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Přepravní kontrola, prosíme, připravte si cestovní doklady.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Ticket inspection. Please have your tickets ready.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H207.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Přepravní kontrola, výstup pouze předními dveřmi. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Přepravní kontrola, prosíme, připravte si cestovní doklady.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Ticket inspection. Please have your tickets ready.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H207.mp3&lt;/mp3&gt;&lt;mp3&gt;H208.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Kočárek přepravujte na určeném místě. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Kočárek přepravujte&amp;lt;br&amp;gt;na určeném místě.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please keep prams in the designated area.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H267.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Pes musí být opatřen náhubkem a vodítkem.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Pes musí být opatřen náhubkem a vodítkem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Dogs must be kept on a leash and wear a muzzle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H433.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Klimatizace v provozu, neotevírejte okna.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Klimatizace v provozu, prosíme,&amp;lt;br&amp;gt; neotevírejte okna.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Air conditioning is operating.&amp;lt;br&amp;gt;Please do not open the windows.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H350.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Porucha, vůz dále nepokračuje. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu technické závady vůz dále nepokračuje.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to a technical failure, this vehicle will not continue its journey.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H148.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Porucha, přestupte do náhradního vozu. &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
+&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu technické závady vůz dále nepokračuje. Prosíme, přestupte do náhradního vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to a technical failure, this vehicle will not continue its journey. Please transfer to a replacement vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H188.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Linka je zde ukončena, neprůjezdnost trasy.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu neprůjezdnosti trasy je linka vedena odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to an obstruction on the route, this line is diverted.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H115.mp3&lt;/mp3&gt;&lt;mp3&gt;H163.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Linka je zkrácena, neprůjezdnost trasy.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu neprůjezdnosti trasy je linka dočasně zkrácena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to an obstruction on the route, this line is shortened.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H115.mp3&lt;/mp3&gt;&lt;mp3&gt;H162.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Provoz metra přerušen, použijte náhradní dopravu.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Provoz metra je přerušen, &amp;lt;br&amp;gt;použijte prosím linky povrchové 
+a náhradní dopravy.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Metro service is suspended.&amp;lt;br&amp;gt;Please use surface transport and replacement lines.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H504.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Provoz tramvají přerušen, použijte náhradní dopravu.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Provoz tramvají přerušen,&amp;lt;br&amp;gt;použijte prosím linky povrchové a náhradní dopravy.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Tram service is suspended. Please use other surface transport and replacement lines.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H923.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vyčkáváme na vzájemný přestup.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for a connecting service.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H284.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Linka jede odklonem, neprůjezdnost trasy.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt; &amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu neprůjezdnosti trasy je linka vedena odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;Due to an obstruction on the route, this line is diverted.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H115.mp3&lt;/mp3&gt;&lt;mp3&gt;H164.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Omluva za zpoždění, špatná průjezdnost trasy.&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme se za zpoždění&amp;lt;br&amp;gt;způsobené špatnou průjezdností trasy.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We apologize for the delay caused by traffic.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H242.mp3&lt;/mp3&gt;&lt;mp3&gt;H280.mp3&lt;/mp3&gt;&lt;mp3&gt;H160.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;změna pásma DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;FareZoneChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;6,8&lt;/changeFrom&gt;&lt;changeTo&gt;7&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;změna linky DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;LineChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;123&lt;/changeFrom&gt;&lt;changeTo&gt;XS2&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Letiště DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Air&amp;quot;&amp;gt;\&amp;lt;/icon&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Odlety&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Flight
 departures&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 1&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
@@ -6242,24 +6871,16 @@
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 2&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;lety do zemí Schengenského prostoru &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ flights to Schengen Area countries&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 3&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;pouze soukromé lety &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ private flights only&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Zpoždění&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Congestion&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme
-          se za zpoždění linky,
-          které je zapříčiněno silnou individiální
-          dopravou a špatnou průjezdností trasy&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-          &amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are sorry for delay
-          caused by heavy traffic and
-          limited passability of roads.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H280.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;změna pásma DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;FareZoneChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;6,8&lt;/changeFrom&gt;&lt;changeTo&gt;7&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;změna linky DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;LineChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;123&lt;/changeFrom&gt;&lt;changeTo&gt;XS2&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;zkrácený spoj DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;Upozorňujeme cestující, že tento spoj končí v zastávce &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please, this bus terminates at &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;  &lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;info o výluce DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font type=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Koh-i-noor – Bělocerkevská&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font type=&amp;quot;48&amp;quot;&amp;gt;Vážení cestující, z důvodu opravy komunikace je linka v tomto úseku odkloněna po náhradní trase. Zastávky Kavkazská, Na Míčánkách a Bělocerkevská jsou vynechány.&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;trvalá změna DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Změna linkového vedení BUS&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;pouze soukromé lety &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ private flights only&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;zkrácený spoj DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;Upozorňujeme cestující, že tento spoj končí v zastávce &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please, this bus terminates at &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;  &lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;info o výluce DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Koh-i-noor – Bělocerkevská&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;Vážení cestující, z důvodu opravy komunikace je linka v tomto úseku odkloněna po náhradní trase. Zastávky Kavkazská, Na Míčánkách a Bělocerkevská jsou vynechány.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;trvalá změna DEMO&lt;/displayName&gt;&lt;duration&gt;15&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Změna linkového vedení BUS&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. září 2018&amp;lt;/b&amp;gt; dochází k trvalé změně linkového vedení
 autobusů PID &amp;lt;b&amp;gt;v oblasti Radotínska&amp;lt;/b&amp;gt;. Podrobnosti naleznete
 na zastávkách a na &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;36&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;
 From saturday, &amp;lt;b&amp;gt;the 1st September 2018&amp;lt;/b&amp;gt;, several permanent changes and modifications
 will take place in operation of the PID system &amp;lt;b&amp;gt;in Radotín area&amp;lt;/b&amp;gt;. Visit &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt; for more
-information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Jiné sdělení DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Zastávky na znamení od 1. 7. 2019&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Jiné sdělení DEMO&lt;/displayName&gt;&lt;duration&gt;15&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Zastávky na znamení od 1. 7. 2019&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. července 2019&amp;lt;/b&amp;gt; budou všechny autobusové zastávky
 na území hl. m. Prahy na znamení. Na autobus není nutné mávat,
 &amp;lt;b&amp;gt;stačí stát viditelně na zastávce&amp;lt;/b&amp;gt;. Před výstupem stiskněte
@@ -6271,15 +6892,9 @@
     &amp;lt;icon type=&amp;quot;c_Exclamation&amp;quot;&amp;gt;!&amp;lt;/icon&amp;gt;
 &amp;lt;/color&amp;gt;    &lt;/icon&gt;&lt;text&gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
 &amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;            
-    Z důvodu sněhové kalamity je ulice Horoměřická neprůjezdná.
-    Linky 316 a 356 jsou ze zastávky Statenice, Černý Vůl, hospoda
-    vedeny odklonem přes zastávky Výhledy, Zemědělská univerzita,
-    V Podbabě a Nádraží Podbaba do zastávky Dejvická (přestup
-    na metro „A“).&amp;lt;br&amp;gt;
-    Pravidelný povoz bude obnoven po zajištění sjízdnosti všech
-    komunikací (během dnešního odpoledne).
+Z důvodu sněhové kalamity je ulice Horoměřická neprůjezdná. Linky 316 a 356 jsou ze zastávky Statenice, Černý Vůl, hospoda vedeny odklonem přes zastávky Výhledy, Zemědělská univerzita, V Podbabě a Nádraží Podbaba do zastávky Dejvická (přestup na metro „A“).&amp;lt;br&amp;gt;Pravidelný povoz bude obnoven po zajištění sjízdnosti všech komunikací (během dnešního odpoledne).
 &amp;lt;/font&amp;gt;
-&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Funkčnost klimatizace&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Vážení cestující, pro správnou funkčnost klimatizace v tomto vozidle, která je nyní v provozu, prosíme neotevírejte boční okna ani stropní poklopy. Děkujeme Vám za pochopení.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H350.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Nastupujte předními dveřmi&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Prosíme, nastupujte předními dveřmi.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H205.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Neprůjezdnost, linka ukončena&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Linka je z důvodu neprůjezdnosti trasy dočasně zkrácena.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H162.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Neprůjezdnost, odklon&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Z důvodu neprůjezdnosti je linka vedena po odklonové trase.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H164.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Přední dveře, předložte doklad&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Nástup předními dveřmi. Předložte prosím jízdní doklad.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H183.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Uvolněte přední dveře&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Uvolněte prosím prostor předních dveří.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H182.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vozidlo obsazeno&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Vozidlo plně obsazeno. Vyčkejte prosím na další spoj.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H201.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;/announcementList&gt;</v>
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Nastupujte předními dveřmi&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Prosíme, nastupujte předními dveřmi.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H205.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Přední dveře, předložte doklad&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Nástup předními dveřmi. Předložte prosím jízdní doklad.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H183.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Uvolněte přední dveře&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Uvolněte prosím prostor předních dveří.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H182.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vozidlo obsazeno&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Vozidlo plně obsazeno. Vyčkejte prosím na další spoj.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H201.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;/announcementList&gt;</v>
       </c>
     </row>
   </sheetData>
@@ -6291,26 +6906,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C152"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.109375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-    </row>
-    <row r="2" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-    </row>
-    <row r="3" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+    </row>
+    <row r="2" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+    </row>
+    <row r="3" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -6321,7 +6936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>5703</v>
       </c>
@@ -6332,7 +6947,7 @@
         <v>34172</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5712</v>
       </c>
@@ -6343,7 +6958,7 @@
         <v>34181</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5736</v>
       </c>
@@ -6354,7 +6969,7 @@
         <v>35954</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5737</v>
       </c>
@@ -6365,7 +6980,7 @@
         <v>35955</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5773</v>
       </c>
@@ -6376,7 +6991,7 @@
         <v>39637</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>5774</v>
       </c>
@@ -6387,7 +7002,7 @@
         <v>39638</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>5866</v>
       </c>
@@ -6398,7 +7013,7 @@
         <v>41798</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>5873</v>
       </c>
@@ -6409,7 +7024,7 @@
         <v>44443</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5909</v>
       </c>
@@ -6420,7 +7035,7 @@
         <v>57613</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>5913</v>
       </c>
@@ -6431,7 +7046,7 @@
         <v>62619</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>5914</v>
       </c>
@@ -6442,7 +7057,7 @@
         <v>62620</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>6975</v>
       </c>
@@ -6453,7 +7068,7 @@
         <v>22614</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>6977</v>
       </c>
@@ -6464,7 +7079,7 @@
         <v>22615</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>7045</v>
       </c>
@@ -6475,7 +7090,7 @@
         <v>3170</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>7046</v>
       </c>
@@ -6486,7 +7101,7 @@
         <v>3171</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>7049</v>
       </c>
@@ -6497,7 +7112,7 @@
         <v>3175</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>7056</v>
       </c>
@@ -6508,7 +7123,7 @@
         <v>3181</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>7438</v>
       </c>
@@ -6519,7 +7134,7 @@
         <v>5369</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>7440</v>
       </c>
@@ -6530,7 +7145,7 @@
         <v>5370</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>7457</v>
       </c>
@@ -6541,7 +7156,7 @@
         <v>6503</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>7459</v>
       </c>
@@ -6552,7 +7167,7 @@
         <v>6505</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>7461</v>
       </c>
@@ -6563,7 +7178,7 @@
         <v>6507</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>7463</v>
       </c>
@@ -6574,7 +7189,7 @@
         <v>6509</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>7466</v>
       </c>
@@ -6585,7 +7200,7 @@
         <v>6512</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>7477</v>
       </c>
@@ -6596,7 +7211,7 @@
         <v>7029</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>7504</v>
       </c>
@@ -6607,7 +7222,7 @@
         <v>9397</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>7510</v>
       </c>
@@ -6618,7 +7233,7 @@
         <v>11109</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>7611</v>
       </c>
@@ -6629,7 +7244,7 @@
         <v>11934</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>7612</v>
       </c>
@@ -6640,7 +7255,7 @@
         <v>11935</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>7613</v>
       </c>
@@ -6651,7 +7266,7 @@
         <v>11936</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>7631</v>
       </c>
@@ -6662,7 +7277,7 @@
         <v>13917</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>7632</v>
       </c>
@@ -6673,7 +7288,7 @@
         <v>13919</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>7634</v>
       </c>
@@ -6684,7 +7299,7 @@
         <v>13921</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>7635</v>
       </c>
@@ -6695,7 +7310,7 @@
         <v>13922</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>7636</v>
       </c>
@@ -6706,7 +7321,7 @@
         <v>13923</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>7637</v>
       </c>
@@ -6717,7 +7332,7 @@
         <v>13924</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>7642</v>
       </c>
@@ -6728,7 +7343,7 @@
         <v>14698</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>7645</v>
       </c>
@@ -6739,7 +7354,7 @@
         <v>14701</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>7669</v>
       </c>
@@ -6750,7 +7365,7 @@
         <v>16251</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>7670</v>
       </c>
@@ -6761,7 +7376,7 @@
         <v>16252</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>7672</v>
       </c>
@@ -6772,7 +7387,7 @@
         <v>16254</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>7676</v>
       </c>
@@ -6783,7 +7398,7 @@
         <v>16257</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>7677</v>
       </c>
@@ -6794,7 +7409,7 @@
         <v>16258</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>7681</v>
       </c>
@@ -6805,7 +7420,7 @@
         <v>16262</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>7715</v>
       </c>
@@ -6816,7 +7431,7 @@
         <v>21072</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>7757</v>
       </c>
@@ -6827,7 +7442,7 @@
         <v>22689</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>7758</v>
       </c>
@@ -6838,7 +7453,7 @@
         <v>22690</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>7760</v>
       </c>
@@ -6849,7 +7464,7 @@
         <v>22692</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>7787</v>
       </c>
@@ -6860,7 +7475,7 @@
         <v>24407</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>7798</v>
       </c>
@@ -6871,7 +7486,7 @@
         <v>25712</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>7993</v>
       </c>
@@ -6882,7 +7497,7 @@
         <v>34136</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>7994</v>
       </c>
@@ -6893,7 +7508,7 @@
         <v>34137</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>9448</v>
       </c>
@@ -6904,7 +7519,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>9515</v>
       </c>
@@ -6915,7 +7530,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>31047</v>
       </c>
@@ -6926,7 +7541,7 @@
         <v>5598</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>31048</v>
       </c>
@@ -6937,7 +7552,7 @@
         <v>41387</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>31050</v>
       </c>
@@ -6948,7 +7563,7 @@
         <v>21206</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>31056</v>
       </c>
@@ -6959,7 +7574,7 @@
         <v>3496</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>31111</v>
       </c>
@@ -6970,7 +7585,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>31308</v>
       </c>
@@ -6981,7 +7596,7 @@
         <v>41699</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>31309</v>
       </c>
@@ -6992,7 +7607,7 @@
         <v>24034</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>31311</v>
       </c>
@@ -7003,7 +7618,7 @@
         <v>40457</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>31312</v>
       </c>
@@ -7014,7 +7629,7 @@
         <v>9424</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>31313</v>
       </c>
@@ -7025,7 +7640,7 @@
         <v>6196</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>31343</v>
       </c>
@@ -7036,7 +7651,7 @@
         <v>65048</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>31344</v>
       </c>
@@ -7047,7 +7662,7 @@
         <v>6194</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>31345</v>
       </c>
@@ -7058,7 +7673,7 @@
         <v>6195</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>31346</v>
       </c>
@@ -7069,7 +7684,7 @@
         <v>3114</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>31347</v>
       </c>
@@ -7080,7 +7695,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>31348</v>
       </c>
@@ -7091,7 +7706,7 @@
         <v>11513</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>31349</v>
       </c>
@@ -7102,7 +7717,7 @@
         <v>27282</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>31350</v>
       </c>
@@ -7113,7 +7728,7 @@
         <v>37573</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>31351</v>
       </c>
@@ -7124,7 +7739,7 @@
         <v>13112</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>31352</v>
       </c>
@@ -7135,7 +7750,7 @@
         <v>41282</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>31353</v>
       </c>
@@ -7146,7 +7761,7 @@
         <v>32548</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>31354</v>
       </c>
@@ -7157,7 +7772,7 @@
         <v>4761</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>31355</v>
       </c>
@@ -7168,7 +7783,7 @@
         <v>4770</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>31356</v>
       </c>
@@ -7179,7 +7794,7 @@
         <v>4226</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>31357</v>
       </c>
@@ -7190,7 +7805,7 @@
         <v>26560</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>31358</v>
       </c>
@@ -7201,7 +7816,7 @@
         <v>11863</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>31359</v>
       </c>
@@ -7212,7 +7827,7 @@
         <v>24055</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>31360</v>
       </c>
@@ -7223,7 +7838,7 @@
         <v>51199</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>31361</v>
       </c>
@@ -7234,7 +7849,7 @@
         <v>24036</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>31362</v>
       </c>
@@ -7245,7 +7860,7 @@
         <v>24041</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>31363</v>
       </c>
@@ -7256,7 +7871,7 @@
         <v>24059</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>31364</v>
       </c>
@@ -7267,7 +7882,7 @@
         <v>34460</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>31365</v>
       </c>
@@ -7278,7 +7893,7 @@
         <v>34461</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>31366</v>
       </c>
@@ -7289,7 +7904,7 @@
         <v>23566</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>31367</v>
       </c>
@@ -7300,7 +7915,7 @@
         <v>4081</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>31368</v>
       </c>
@@ -7311,7 +7926,7 @@
         <v>29525</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>31369</v>
       </c>
@@ -7322,7 +7937,7 @@
         <v>29523</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>31370</v>
       </c>
@@ -7333,7 +7948,7 @@
         <v>29524</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>31371</v>
       </c>
@@ -7344,7 +7959,7 @@
         <v>21211</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>31372</v>
       </c>
@@ -7355,7 +7970,7 @@
         <v>21208</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>31374</v>
       </c>
@@ -7366,7 +7981,7 @@
         <v>21219</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>31375</v>
       </c>
@@ -7377,7 +7992,7 @@
         <v>24001</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>31376</v>
       </c>
@@ -7388,7 +8003,7 @@
         <v>19660</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>31377</v>
       </c>
@@ -7399,7 +8014,7 @@
         <v>33405</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>31378</v>
       </c>
@@ -7410,7 +8025,7 @@
         <v>33413</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>31379</v>
       </c>
@@ -7421,7 +8036,7 @@
         <v>66367</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>31380</v>
       </c>
@@ -7432,7 +8047,7 @@
         <v>12480</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>31381</v>
       </c>
@@ -7443,7 +8058,7 @@
         <v>12485</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>31382</v>
       </c>
@@ -7454,7 +8069,7 @@
         <v>53705</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>31383</v>
       </c>
@@ -7465,7 +8080,7 @@
         <v>6692</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>31384</v>
       </c>
@@ -7476,7 +8091,7 @@
         <v>6693</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>31385</v>
       </c>
@@ -7487,7 +8102,7 @@
         <v>38300</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>31386</v>
       </c>
@@ -7498,7 +8113,7 @@
         <v>38308</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>31387</v>
       </c>
@@ -7509,7 +8124,7 @@
         <v>38297</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>31388</v>
       </c>
@@ -7520,7 +8135,7 @@
         <v>38293</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>31389</v>
       </c>
@@ -7531,7 +8146,7 @@
         <v>38316</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>31390</v>
       </c>
@@ -7542,7 +8157,7 @@
         <v>30530</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>31391</v>
       </c>
@@ -7553,7 +8168,7 @@
         <v>30526</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>31392</v>
       </c>
@@ -7564,7 +8179,7 @@
         <v>30536</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>31511</v>
       </c>
@@ -7575,7 +8190,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>31514</v>
       </c>
@@ -7586,7 +8201,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>31535</v>
       </c>
@@ -7597,7 +8212,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>31536</v>
       </c>
@@ -7608,7 +8223,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>31540</v>
       </c>
@@ -7619,7 +8234,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>31595</v>
       </c>
@@ -7630,7 +8245,7 @@
         <v>9384</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>31609</v>
       </c>
@@ -7641,7 +8256,7 @@
         <v>10763</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>31646</v>
       </c>
@@ -7652,7 +8267,7 @@
         <v>13657</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>31647</v>
       </c>
@@ -7663,7 +8278,7 @@
         <v>13660</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>31648</v>
       </c>
@@ -7674,7 +8289,7 @@
         <v>13661</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>31651</v>
       </c>
@@ -7685,7 +8300,7 @@
         <v>14696</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>31665</v>
       </c>
@@ -7696,7 +8311,7 @@
         <v>15801</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>31670</v>
       </c>
@@ -7707,7 +8322,7 @@
         <v>15808</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>31672</v>
       </c>
@@ -7718,7 +8333,7 @@
         <v>15811</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>31675</v>
       </c>
@@ -7729,7 +8344,7 @@
         <v>15818</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>31676</v>
       </c>
@@ -7740,7 +8355,7 @@
         <v>15819</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>31724</v>
       </c>
@@ -7751,7 +8366,7 @@
         <v>21083</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>31726</v>
       </c>
@@ -7762,7 +8377,7 @@
         <v>21093</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>31743</v>
       </c>
@@ -7773,7 +8388,7 @@
         <v>21365</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>31747</v>
       </c>
@@ -7784,7 +8399,7 @@
         <v>22390</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>31748</v>
       </c>
@@ -7795,7 +8410,7 @@
         <v>22392</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>31749</v>
       </c>
@@ -7806,7 +8421,7 @@
         <v>13663</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>31749</v>
       </c>
@@ -7817,7 +8432,7 @@
         <v>22394</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>31866</v>
       </c>
@@ -7828,7 +8443,7 @@
         <v>34237</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>31883</v>
       </c>
@@ -7839,7 +8454,7 @@
         <v>37934</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>31884</v>
       </c>
@@ -7850,7 +8465,7 @@
         <v>37935</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>31889</v>
       </c>
@@ -7861,7 +8476,7 @@
         <v>38964</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>159</v>
       </c>
@@ -7872,7 +8487,7 @@
         <v>3176</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>152</v>
       </c>
@@ -7883,7 +8498,7 @@
         <v>3177</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>158</v>
       </c>
@@ -7894,7 +8509,7 @@
         <v>3172</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>154</v>
       </c>
@@ -7905,7 +8520,7 @@
         <v>3174</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>150</v>
       </c>
@@ -7916,7 +8531,7 @@
         <v>3178</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>59</v>
       </c>
@@ -7927,7 +8542,7 @@
         <v>10755</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>60</v>
       </c>
@@ -7938,7 +8553,7 @@
         <v>10761</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>61</v>
       </c>
@@ -7949,7 +8564,7 @@
         <v>15513</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>160</v>
       </c>
@@ -7992,129 +8607,129 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+    <row r="5" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
+    <row r="6" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+    <row r="7" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
+    <row r="8" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
+    <row r="9" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
+    <row r="10" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
+    <row r="11" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
+    <row r="12" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+    <row r="13" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
+    <row r="14" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="17" t="s">
+    <row r="15" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
+    <row r="16" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="17" t="s">
+    <row r="17" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="17" t="s">
+    <row r="18" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="17" t="s">
+    <row r="19" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="17" t="s">
+    <row r="20" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18" s="17" t="s">
+    <row r="21" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="17" t="s">
+    <row r="22" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20" s="17" t="s">
+    <row r="23" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="17" t="s">
+    <row r="24" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
         <v>550</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="17" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A23" s="17" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A24" s="18" t="s">
-        <v>553</v>
       </c>
     </row>
   </sheetData>
